--- a/public/templates/cs34.xlsx
+++ b/public/templates/cs34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CCE35F-4147-44C9-ABD9-C739BBCECE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4259C62C-171C-4C4C-8776-CB937818F6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Central" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Central!$A$1:$CA$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Central!$A$1:$CJ$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
   <si>
     <t>Nº</t>
   </si>
@@ -1272,6 +1272,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1279,81 +1354,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1430,7 +1430,17 @@
     <cellStyle name="Title" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Warning Text" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1948,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CD54"/>
+  <dimension ref="A2:CJ54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
@@ -1956,442 +1966,520 @@
     <col min="3" max="58" width="4" customWidth="1"/>
     <col min="59" max="59" width="3.88671875" customWidth="1"/>
     <col min="60" max="60" width="29.44140625" customWidth="1"/>
-    <col min="61" max="72" width="4.44140625" customWidth="1"/>
-    <col min="73" max="75" width="4.6640625" customWidth="1"/>
-    <col min="76" max="81" width="4.5546875" customWidth="1"/>
+    <col min="61" max="88" width="4.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A2" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Y2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="83"/>
-      <c r="AN2" s="83"/>
-      <c r="AO2" s="83"/>
-      <c r="AP2" s="83"/>
-      <c r="AQ2" s="83"/>
-      <c r="AR2" s="83"/>
-      <c r="AS2" s="83"/>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="83"/>
-      <c r="AY2" s="83"/>
-      <c r="AZ2" s="83"/>
-      <c r="BA2" s="83"/>
-      <c r="BB2" s="83"/>
-      <c r="BC2" s="83"/>
-      <c r="BD2" s="83"/>
-      <c r="BE2" s="83"/>
-      <c r="BF2" s="83"/>
-      <c r="BG2" s="83" t="str">
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
+      <c r="Y2" s="92"/>
+      <c r="Z2" s="92"/>
+      <c r="AA2" s="92"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="92"/>
+      <c r="AD2" s="92"/>
+      <c r="AE2" s="92"/>
+      <c r="AF2" s="92"/>
+      <c r="AG2" s="92"/>
+      <c r="AH2" s="92"/>
+      <c r="AI2" s="92"/>
+      <c r="AJ2" s="92"/>
+      <c r="AK2" s="92"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="92"/>
+      <c r="AO2" s="92"/>
+      <c r="AP2" s="92"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="92"/>
+      <c r="AS2" s="92"/>
+      <c r="AT2" s="92"/>
+      <c r="AU2" s="92"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="92"/>
+      <c r="AX2" s="92"/>
+      <c r="AY2" s="92"/>
+      <c r="AZ2" s="92"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="92"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="92" t="str">
         <f>A2</f>
         <v>CUADRO GENERAL DE NOTAS</v>
       </c>
-      <c r="BH2" s="83"/>
-      <c r="BI2" s="83"/>
-      <c r="BJ2" s="83"/>
-      <c r="BK2" s="83"/>
-      <c r="BL2" s="83"/>
-      <c r="BM2" s="83"/>
-      <c r="BN2" s="83"/>
-      <c r="BO2" s="83"/>
-      <c r="BP2" s="83"/>
-      <c r="BQ2" s="83"/>
-      <c r="BR2" s="83"/>
-      <c r="BS2" s="83"/>
-      <c r="BT2" s="83"/>
+      <c r="BH2" s="92"/>
+      <c r="BI2" s="92"/>
+      <c r="BJ2" s="92"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="92"/>
+      <c r="BM2" s="92"/>
+      <c r="BN2" s="92"/>
+      <c r="BO2" s="92"/>
+      <c r="BP2" s="92"/>
+      <c r="BQ2" s="92"/>
+      <c r="BR2" s="92"/>
+      <c r="BS2" s="92"/>
+      <c r="BT2" s="92"/>
+      <c r="BU2" s="92"/>
+      <c r="BV2" s="92"/>
+      <c r="BW2" s="92"/>
+      <c r="BX2" s="92"/>
+      <c r="BY2" s="92"/>
+      <c r="BZ2" s="92"/>
+      <c r="CA2" s="92"/>
+      <c r="CB2" s="92"/>
+      <c r="CC2" s="92"/>
+      <c r="CD2" s="92"/>
+      <c r="CE2" s="92"/>
+      <c r="CF2" s="92"/>
+      <c r="CG2" s="92"/>
+      <c r="CH2" s="92"/>
+      <c r="CI2" s="92"/>
+      <c r="CJ2" s="92"/>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A3" s="84" t="s">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A3" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="84"/>
-      <c r="AD3" s="84"/>
-      <c r="AE3" s="84"/>
-      <c r="AF3" s="84"/>
-      <c r="AG3" s="84"/>
-      <c r="AH3" s="84"/>
-      <c r="AI3" s="84"/>
-      <c r="AJ3" s="84"/>
-      <c r="AK3" s="84"/>
-      <c r="AL3" s="84"/>
-      <c r="AM3" s="84"/>
-      <c r="AN3" s="84"/>
-      <c r="AO3" s="84"/>
-      <c r="AP3" s="84"/>
-      <c r="AQ3" s="84"/>
-      <c r="AR3" s="84"/>
-      <c r="AS3" s="84"/>
-      <c r="AT3" s="84"/>
-      <c r="AU3" s="84"/>
-      <c r="AV3" s="84"/>
-      <c r="AW3" s="84"/>
-      <c r="AX3" s="84"/>
-      <c r="AY3" s="84"/>
-      <c r="AZ3" s="84"/>
-      <c r="BA3" s="84"/>
-      <c r="BB3" s="84"/>
-      <c r="BC3" s="84"/>
-      <c r="BD3" s="84"/>
-      <c r="BE3" s="84"/>
-      <c r="BF3" s="84"/>
-      <c r="BG3" s="84" t="str">
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="93"/>
+      <c r="AF3" s="93"/>
+      <c r="AG3" s="93"/>
+      <c r="AH3" s="93"/>
+      <c r="AI3" s="93"/>
+      <c r="AJ3" s="93"/>
+      <c r="AK3" s="93"/>
+      <c r="AL3" s="93"/>
+      <c r="AM3" s="93"/>
+      <c r="AN3" s="93"/>
+      <c r="AO3" s="93"/>
+      <c r="AP3" s="93"/>
+      <c r="AQ3" s="93"/>
+      <c r="AR3" s="93"/>
+      <c r="AS3" s="93"/>
+      <c r="AT3" s="93"/>
+      <c r="AU3" s="93"/>
+      <c r="AV3" s="93"/>
+      <c r="AW3" s="93"/>
+      <c r="AX3" s="93"/>
+      <c r="AY3" s="93"/>
+      <c r="AZ3" s="93"/>
+      <c r="BA3" s="93"/>
+      <c r="BB3" s="93"/>
+      <c r="BC3" s="93"/>
+      <c r="BD3" s="93"/>
+      <c r="BE3" s="93"/>
+      <c r="BF3" s="93"/>
+      <c r="BG3" s="93" t="str">
         <f t="shared" ref="BG3:BG4" si="0">A3</f>
         <v>(CONSEJEROS Y DIRECCIONES TÉCNICAS)</v>
       </c>
-      <c r="BH3" s="84"/>
-      <c r="BI3" s="84"/>
-      <c r="BJ3" s="84"/>
-      <c r="BK3" s="84"/>
-      <c r="BL3" s="84"/>
-      <c r="BM3" s="84"/>
-      <c r="BN3" s="84"/>
-      <c r="BO3" s="84"/>
-      <c r="BP3" s="84"/>
-      <c r="BQ3" s="84"/>
-      <c r="BR3" s="84"/>
-      <c r="BS3" s="84"/>
-      <c r="BT3" s="84"/>
+      <c r="BH3" s="93"/>
+      <c r="BI3" s="93"/>
+      <c r="BJ3" s="93"/>
+      <c r="BK3" s="93"/>
+      <c r="BL3" s="93"/>
+      <c r="BM3" s="93"/>
+      <c r="BN3" s="93"/>
+      <c r="BO3" s="93"/>
+      <c r="BP3" s="93"/>
+      <c r="BQ3" s="93"/>
+      <c r="BR3" s="93"/>
+      <c r="BS3" s="93"/>
+      <c r="BT3" s="93"/>
+      <c r="BU3" s="93"/>
+      <c r="BV3" s="93"/>
+      <c r="BW3" s="93"/>
+      <c r="BX3" s="93"/>
+      <c r="BY3" s="93"/>
+      <c r="BZ3" s="93"/>
+      <c r="CA3" s="93"/>
+      <c r="CB3" s="93"/>
+      <c r="CC3" s="93"/>
+      <c r="CD3" s="93"/>
+      <c r="CE3" s="93"/>
+      <c r="CF3" s="93"/>
+      <c r="CG3" s="93"/>
+      <c r="CH3" s="93"/>
+      <c r="CI3" s="93"/>
+      <c r="CJ3" s="93"/>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="85"/>
-      <c r="AD4" s="85"/>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="85"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="85"/>
-      <c r="AR4" s="85"/>
-      <c r="AS4" s="85"/>
-      <c r="AT4" s="85"/>
-      <c r="AU4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="85"/>
-      <c r="AY4" s="85"/>
-      <c r="AZ4" s="85"/>
-      <c r="BA4" s="85"/>
-      <c r="BB4" s="85"/>
-      <c r="BC4" s="85"/>
-      <c r="BD4" s="85"/>
-      <c r="BE4" s="85"/>
-      <c r="BF4" s="85"/>
-      <c r="BG4" s="85">
+    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A4" s="94"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="94"/>
+      <c r="AQ4" s="94"/>
+      <c r="AR4" s="94"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94"/>
+      <c r="BA4" s="94"/>
+      <c r="BB4" s="94"/>
+      <c r="BC4" s="94"/>
+      <c r="BD4" s="94"/>
+      <c r="BE4" s="94"/>
+      <c r="BF4" s="94"/>
+      <c r="BG4" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BH4" s="85"/>
-      <c r="BI4" s="85"/>
-      <c r="BJ4" s="85"/>
-      <c r="BK4" s="85"/>
-      <c r="BL4" s="85"/>
-      <c r="BM4" s="85"/>
-      <c r="BN4" s="85"/>
-      <c r="BO4" s="85"/>
-      <c r="BP4" s="85"/>
-      <c r="BQ4" s="85"/>
-      <c r="BR4" s="85"/>
-      <c r="BS4" s="85"/>
-      <c r="BT4" s="85"/>
+      <c r="BH4" s="94"/>
+      <c r="BI4" s="94"/>
+      <c r="BJ4" s="94"/>
+      <c r="BK4" s="94"/>
+      <c r="BL4" s="94"/>
+      <c r="BM4" s="94"/>
+      <c r="BN4" s="94"/>
+      <c r="BO4" s="94"/>
+      <c r="BP4" s="94"/>
+      <c r="BQ4" s="94"/>
+      <c r="BR4" s="94"/>
+      <c r="BS4" s="94"/>
+      <c r="BT4" s="94"/>
+      <c r="BU4" s="94"/>
+      <c r="BV4" s="94"/>
+      <c r="BW4" s="94"/>
+      <c r="BX4" s="94"/>
+      <c r="BY4" s="94"/>
+      <c r="BZ4" s="94"/>
+      <c r="CA4" s="94"/>
+      <c r="CB4" s="94"/>
+      <c r="CC4" s="94"/>
+      <c r="CD4" s="94"/>
+      <c r="CE4" s="94"/>
+      <c r="CF4" s="94"/>
+      <c r="CG4" s="94"/>
+      <c r="CH4" s="94"/>
+      <c r="CI4" s="94"/>
+      <c r="CJ4" s="94"/>
     </row>
-    <row r="5" spans="1:72" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="86"/>
-      <c r="V5" s="86"/>
-      <c r="W5" s="86"/>
-      <c r="X5" s="86"/>
-      <c r="Y5" s="86"/>
-      <c r="Z5" s="86"/>
-      <c r="AA5" s="86"/>
-      <c r="AB5" s="86"/>
-      <c r="AC5" s="86"/>
-      <c r="AD5" s="86"/>
-      <c r="AE5" s="86"/>
-      <c r="AF5" s="86"/>
-      <c r="AG5" s="86"/>
-      <c r="AH5" s="86"/>
-      <c r="AI5" s="86"/>
-      <c r="AJ5" s="86"/>
-      <c r="AK5" s="86"/>
-      <c r="AL5" s="86"/>
-      <c r="AM5" s="86"/>
-      <c r="AN5" s="86"/>
-      <c r="AO5" s="86"/>
-      <c r="AP5" s="86"/>
-      <c r="AQ5" s="86"/>
-      <c r="AR5" s="86"/>
-      <c r="AS5" s="86"/>
-      <c r="AT5" s="86"/>
-      <c r="AU5" s="86"/>
-      <c r="AV5" s="86"/>
-      <c r="AW5" s="86"/>
-      <c r="AX5" s="86"/>
-      <c r="AY5" s="86"/>
-      <c r="AZ5" s="86"/>
-      <c r="BA5" s="86"/>
-      <c r="BB5" s="86"/>
-      <c r="BC5" s="86"/>
-      <c r="BD5" s="86"/>
-      <c r="BE5" s="86"/>
-      <c r="BF5" s="86"/>
-      <c r="BG5" s="86">
+    <row r="5" spans="1:88" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
+      <c r="S5" s="95"/>
+      <c r="T5" s="95"/>
+      <c r="U5" s="95"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="95"/>
+      <c r="X5" s="95"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="95"/>
+      <c r="AA5" s="95"/>
+      <c r="AB5" s="95"/>
+      <c r="AC5" s="95"/>
+      <c r="AD5" s="95"/>
+      <c r="AE5" s="95"/>
+      <c r="AF5" s="95"/>
+      <c r="AG5" s="95"/>
+      <c r="AH5" s="95"/>
+      <c r="AI5" s="95"/>
+      <c r="AJ5" s="95"/>
+      <c r="AK5" s="95"/>
+      <c r="AL5" s="95"/>
+      <c r="AM5" s="95"/>
+      <c r="AN5" s="95"/>
+      <c r="AO5" s="95"/>
+      <c r="AP5" s="95"/>
+      <c r="AQ5" s="95"/>
+      <c r="AR5" s="95"/>
+      <c r="AS5" s="95"/>
+      <c r="AT5" s="95"/>
+      <c r="AU5" s="95"/>
+      <c r="AV5" s="95"/>
+      <c r="AW5" s="95"/>
+      <c r="AX5" s="95"/>
+      <c r="AY5" s="95"/>
+      <c r="AZ5" s="95"/>
+      <c r="BA5" s="95"/>
+      <c r="BB5" s="95"/>
+      <c r="BC5" s="95"/>
+      <c r="BD5" s="95"/>
+      <c r="BE5" s="95"/>
+      <c r="BF5" s="95"/>
+      <c r="BG5" s="95">
         <f>A5</f>
         <v>0</v>
       </c>
-      <c r="BH5" s="86"/>
-      <c r="BI5" s="86"/>
-      <c r="BJ5" s="86"/>
-      <c r="BK5" s="86"/>
-      <c r="BL5" s="86"/>
-      <c r="BM5" s="86"/>
-      <c r="BN5" s="86"/>
-      <c r="BO5" s="86"/>
-      <c r="BP5" s="86"/>
-      <c r="BQ5" s="86"/>
-      <c r="BR5" s="86"/>
-      <c r="BS5" s="86"/>
-      <c r="BT5" s="86"/>
+      <c r="BH5" s="95"/>
+      <c r="BI5" s="95"/>
+      <c r="BJ5" s="95"/>
+      <c r="BK5" s="95"/>
+      <c r="BL5" s="95"/>
+      <c r="BM5" s="95"/>
+      <c r="BN5" s="95"/>
+      <c r="BO5" s="95"/>
+      <c r="BP5" s="95"/>
+      <c r="BQ5" s="95"/>
+      <c r="BR5" s="95"/>
+      <c r="BS5" s="95"/>
+      <c r="BT5" s="95"/>
+      <c r="BU5" s="95"/>
+      <c r="BV5" s="95"/>
+      <c r="BW5" s="95"/>
+      <c r="BX5" s="95"/>
+      <c r="BY5" s="95"/>
+      <c r="BZ5" s="95"/>
+      <c r="CA5" s="95"/>
+      <c r="CB5" s="95"/>
+      <c r="CC5" s="95"/>
+      <c r="CD5" s="95"/>
+      <c r="CE5" s="95"/>
+      <c r="CF5" s="95"/>
+      <c r="CG5" s="95"/>
+      <c r="CH5" s="95"/>
+      <c r="CI5" s="95"/>
+      <c r="CJ5" s="95"/>
     </row>
-    <row r="6" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A6" s="87" t="s">
+    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A6" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="80"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="79" t="s">
+      <c r="D6" s="81"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="79" t="s">
+      <c r="H6" s="81"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="80"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="80" t="s">
+      <c r="L6" s="81"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="79" t="s">
+      <c r="P6" s="81"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="80"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="79" t="s">
+      <c r="T6" s="81"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="80" t="s">
+      <c r="X6" s="81"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="AB6" s="80"/>
-      <c r="AC6" s="81"/>
-      <c r="AD6" s="97"/>
-      <c r="AE6" s="79" t="s">
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="96"/>
+      <c r="AE6" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="AF6" s="80"/>
-      <c r="AG6" s="81"/>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="79" t="s">
+      <c r="AF6" s="81"/>
+      <c r="AG6" s="82"/>
+      <c r="AH6" s="83"/>
+      <c r="AI6" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="AJ6" s="80"/>
-      <c r="AK6" s="81"/>
-      <c r="AL6" s="82"/>
-      <c r="AM6" s="79" t="s">
+      <c r="AJ6" s="81"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="83"/>
+      <c r="AM6" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="80"/>
-      <c r="AO6" s="81"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="79" t="s">
+      <c r="AN6" s="81"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="83"/>
+      <c r="AQ6" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="AR6" s="80"/>
-      <c r="AS6" s="81"/>
-      <c r="AT6" s="82"/>
-      <c r="AU6" s="79" t="s">
+      <c r="AR6" s="81"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="83"/>
+      <c r="AU6" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="AV6" s="80"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="80" t="s">
+      <c r="AV6" s="81"/>
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="83"/>
+      <c r="AY6" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="AZ6" s="80"/>
-      <c r="BA6" s="81"/>
-      <c r="BB6" s="97"/>
-      <c r="BC6" s="98" t="s">
+      <c r="AZ6" s="81"/>
+      <c r="BA6" s="82"/>
+      <c r="BB6" s="96"/>
+      <c r="BC6" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="BD6" s="99"/>
-      <c r="BE6" s="100"/>
-      <c r="BF6" s="101"/>
-      <c r="BG6" s="87" t="s">
+      <c r="BD6" s="98"/>
+      <c r="BE6" s="99"/>
+      <c r="BF6" s="100"/>
+      <c r="BG6" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="BH6" s="89" t="s">
+      <c r="BH6" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="BI6" s="76" t="s">
+      <c r="BI6" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="BJ6" s="77"/>
-      <c r="BK6" s="77"/>
-      <c r="BL6" s="77"/>
-      <c r="BM6" s="76" t="s">
+      <c r="BJ6" s="102"/>
+      <c r="BK6" s="102"/>
+      <c r="BL6" s="102"/>
+      <c r="BM6" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="BN6" s="77"/>
-      <c r="BO6" s="77"/>
-      <c r="BP6" s="78"/>
-      <c r="BQ6" s="79" t="s">
+      <c r="BN6" s="102"/>
+      <c r="BO6" s="102"/>
+      <c r="BP6" s="103"/>
+      <c r="BQ6" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="BR6" s="80"/>
-      <c r="BS6" s="81"/>
-      <c r="BT6" s="82"/>
+      <c r="BR6" s="81"/>
+      <c r="BS6" s="82"/>
+      <c r="BT6" s="83"/>
+      <c r="BU6" s="101"/>
+      <c r="BV6" s="102"/>
+      <c r="BW6" s="102"/>
+      <c r="BX6" s="102"/>
+      <c r="BY6" s="101"/>
+      <c r="BZ6" s="102"/>
+      <c r="CA6" s="102"/>
+      <c r="CB6" s="103"/>
+      <c r="CC6" s="101"/>
+      <c r="CD6" s="102"/>
+      <c r="CE6" s="102"/>
+      <c r="CF6" s="102"/>
+      <c r="CG6" s="101"/>
+      <c r="CH6" s="102"/>
+      <c r="CI6" s="102"/>
+      <c r="CJ6" s="103"/>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A7" s="85"/>
+      <c r="B7" s="87"/>
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2560,8 +2648,8 @@
       <c r="BF7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="BG7" s="88"/>
-      <c r="BH7" s="90"/>
+      <c r="BG7" s="85"/>
+      <c r="BH7" s="87"/>
       <c r="BI7" s="11" t="s">
         <v>26</v>
       </c>
@@ -2598,8 +2686,56 @@
       <c r="BT7" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="BU7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BV7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BX7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="BY7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="BZ7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CB7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="CC7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="CE7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CF7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="CG7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="CH7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="CI7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CJ7" s="15" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <v>1</v>
       </c>
@@ -2739,8 +2875,36 @@
         <f t="shared" ref="BT8:BT37" si="17">IF(SUM(BQ8:BS8)=0,"",ROUND(AVERAGE(BQ8:BS8),0))</f>
         <v/>
       </c>
+      <c r="BU8" s="29"/>
+      <c r="BV8" s="27"/>
+      <c r="BW8" s="28"/>
+      <c r="BX8" s="30" t="str">
+        <f t="shared" ref="BX8:BX37" si="18">IF(SUM(BU8:BW8)=0,"",ROUND(AVERAGE(BU8:BW8),0))</f>
+        <v/>
+      </c>
+      <c r="BY8" s="29"/>
+      <c r="BZ8" s="27"/>
+      <c r="CA8" s="28"/>
+      <c r="CB8" s="30" t="str">
+        <f t="shared" ref="CB8:CB37" si="19">IF(SUM(BY8:CA8)=0,"",ROUND(AVERAGE(BY8:CA8),0))</f>
+        <v/>
+      </c>
+      <c r="CC8" s="29"/>
+      <c r="CD8" s="27"/>
+      <c r="CE8" s="28"/>
+      <c r="CF8" s="30" t="str">
+        <f t="shared" ref="CF8:CF37" si="20">IF(SUM(CC8:CE8)=0,"",ROUND(AVERAGE(CC8:CE8),0))</f>
+        <v/>
+      </c>
+      <c r="CG8" s="29"/>
+      <c r="CH8" s="27"/>
+      <c r="CI8" s="28"/>
+      <c r="CJ8" s="30" t="str">
+        <f t="shared" ref="CJ8:CJ37" si="21">IF(SUM(CG8:CI8)=0,"",ROUND(AVERAGE(CG8:CI8),0))</f>
+        <v/>
+      </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>2</v>
       </c>
@@ -2753,19 +2917,19 @@
         <v/>
       </c>
       <c r="G9" s="34" t="str">
-        <f t="shared" ref="G9:G37" si="18">IF(BQ9="","",BQ9)</f>
+        <f t="shared" ref="G9:G37" si="22">IF(BQ9="","",BQ9)</f>
         <v/>
       </c>
       <c r="H9" s="34" t="str">
-        <f t="shared" ref="H9:H37" si="19">IF(BR9="","",BR9)</f>
+        <f t="shared" ref="H9:H37" si="23">IF(BR9="","",BR9)</f>
         <v/>
       </c>
       <c r="I9" s="35" t="str">
-        <f t="shared" ref="I9:I37" si="20">IF(BS9="","",BS9)</f>
+        <f t="shared" ref="I9:I37" si="24">IF(BS9="","",BS9)</f>
         <v/>
       </c>
       <c r="J9" s="37" t="str">
-        <f t="shared" ref="J9:J37" si="21">IF(BT9="","",BT9)</f>
+        <f t="shared" ref="J9:J37" si="25">IF(BT9="","",BT9)</f>
         <v/>
       </c>
       <c r="K9" s="33"/>
@@ -2856,7 +3020,7 @@
         <v>2</v>
       </c>
       <c r="BH9" s="32" t="str">
-        <f t="shared" ref="BH9:BH37" si="22">IF(B9="","",B9)</f>
+        <f t="shared" ref="BH9:BH37" si="26">IF(B9="","",B9)</f>
         <v/>
       </c>
       <c r="BI9" s="44"/>
@@ -2880,8 +3044,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU9" s="44"/>
+      <c r="BV9" s="42"/>
+      <c r="BW9" s="43"/>
+      <c r="BX9" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY9" s="44"/>
+      <c r="BZ9" s="42"/>
+      <c r="CA9" s="43"/>
+      <c r="CB9" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC9" s="44"/>
+      <c r="CD9" s="42"/>
+      <c r="CE9" s="43"/>
+      <c r="CF9" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG9" s="44"/>
+      <c r="CH9" s="42"/>
+      <c r="CI9" s="43"/>
+      <c r="CJ9" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
         <v>3</v>
       </c>
@@ -2894,19 +3086,19 @@
         <v/>
       </c>
       <c r="G10" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H10" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I10" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J10" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K10" s="33"/>
@@ -2997,7 +3189,7 @@
         <v>3</v>
       </c>
       <c r="BH10" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI10" s="44"/>
@@ -3021,8 +3213,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU10" s="44"/>
+      <c r="BV10" s="42"/>
+      <c r="BW10" s="43"/>
+      <c r="BX10" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY10" s="44"/>
+      <c r="BZ10" s="42"/>
+      <c r="CA10" s="43"/>
+      <c r="CB10" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC10" s="44"/>
+      <c r="CD10" s="42"/>
+      <c r="CE10" s="43"/>
+      <c r="CF10" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG10" s="44"/>
+      <c r="CH10" s="42"/>
+      <c r="CI10" s="43"/>
+      <c r="CJ10" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
         <v>4</v>
       </c>
@@ -3035,19 +3255,19 @@
         <v/>
       </c>
       <c r="G11" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H11" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I11" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J11" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K11" s="33"/>
@@ -3138,7 +3358,7 @@
         <v>4</v>
       </c>
       <c r="BH11" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI11" s="44"/>
@@ -3162,8 +3382,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU11" s="44"/>
+      <c r="BV11" s="42"/>
+      <c r="BW11" s="43"/>
+      <c r="BX11" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY11" s="44"/>
+      <c r="BZ11" s="42"/>
+      <c r="CA11" s="43"/>
+      <c r="CB11" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC11" s="44"/>
+      <c r="CD11" s="42"/>
+      <c r="CE11" s="43"/>
+      <c r="CF11" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG11" s="44"/>
+      <c r="CH11" s="42"/>
+      <c r="CI11" s="43"/>
+      <c r="CJ11" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A12" s="31">
         <v>5</v>
       </c>
@@ -3176,19 +3424,19 @@
         <v/>
       </c>
       <c r="G12" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H12" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I12" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J12" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K12" s="33"/>
@@ -3279,7 +3527,7 @@
         <v>5</v>
       </c>
       <c r="BH12" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI12" s="44"/>
@@ -3303,8 +3551,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU12" s="44"/>
+      <c r="BV12" s="42"/>
+      <c r="BW12" s="43"/>
+      <c r="BX12" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY12" s="44"/>
+      <c r="BZ12" s="42"/>
+      <c r="CA12" s="43"/>
+      <c r="CB12" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC12" s="44"/>
+      <c r="CD12" s="42"/>
+      <c r="CE12" s="43"/>
+      <c r="CF12" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG12" s="44"/>
+      <c r="CH12" s="42"/>
+      <c r="CI12" s="43"/>
+      <c r="CJ12" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A13" s="31">
         <v>6</v>
       </c>
@@ -3317,19 +3593,19 @@
         <v/>
       </c>
       <c r="G13" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H13" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I13" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J13" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K13" s="33"/>
@@ -3420,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="BH13" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI13" s="44"/>
@@ -3444,8 +3720,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU13" s="44"/>
+      <c r="BV13" s="42"/>
+      <c r="BW13" s="43"/>
+      <c r="BX13" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY13" s="44"/>
+      <c r="BZ13" s="42"/>
+      <c r="CA13" s="43"/>
+      <c r="CB13" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC13" s="44"/>
+      <c r="CD13" s="42"/>
+      <c r="CE13" s="43"/>
+      <c r="CF13" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG13" s="44"/>
+      <c r="CH13" s="42"/>
+      <c r="CI13" s="43"/>
+      <c r="CJ13" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A14" s="31">
         <v>7</v>
       </c>
@@ -3458,19 +3762,19 @@
         <v/>
       </c>
       <c r="G14" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H14" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I14" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J14" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K14" s="33"/>
@@ -3561,7 +3865,7 @@
         <v>7</v>
       </c>
       <c r="BH14" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI14" s="44"/>
@@ -3585,8 +3889,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU14" s="44"/>
+      <c r="BV14" s="42"/>
+      <c r="BW14" s="43"/>
+      <c r="BX14" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY14" s="44"/>
+      <c r="BZ14" s="42"/>
+      <c r="CA14" s="43"/>
+      <c r="CB14" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC14" s="44"/>
+      <c r="CD14" s="42"/>
+      <c r="CE14" s="43"/>
+      <c r="CF14" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG14" s="44"/>
+      <c r="CH14" s="42"/>
+      <c r="CI14" s="43"/>
+      <c r="CJ14" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A15" s="31">
         <v>8</v>
       </c>
@@ -3599,19 +3931,19 @@
         <v/>
       </c>
       <c r="G15" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H15" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I15" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J15" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K15" s="33"/>
@@ -3702,7 +4034,7 @@
         <v>8</v>
       </c>
       <c r="BH15" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI15" s="44"/>
@@ -3726,8 +4058,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU15" s="44"/>
+      <c r="BV15" s="42"/>
+      <c r="BW15" s="43"/>
+      <c r="BX15" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY15" s="44"/>
+      <c r="BZ15" s="42"/>
+      <c r="CA15" s="43"/>
+      <c r="CB15" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC15" s="44"/>
+      <c r="CD15" s="42"/>
+      <c r="CE15" s="43"/>
+      <c r="CF15" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG15" s="44"/>
+      <c r="CH15" s="42"/>
+      <c r="CI15" s="43"/>
+      <c r="CJ15" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>9</v>
       </c>
@@ -3740,19 +4100,19 @@
         <v/>
       </c>
       <c r="G16" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H16" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I16" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J16" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K16" s="33"/>
@@ -3843,7 +4203,7 @@
         <v>9</v>
       </c>
       <c r="BH16" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI16" s="44"/>
@@ -3867,8 +4227,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU16" s="44"/>
+      <c r="BV16" s="42"/>
+      <c r="BW16" s="43"/>
+      <c r="BX16" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY16" s="44"/>
+      <c r="BZ16" s="42"/>
+      <c r="CA16" s="43"/>
+      <c r="CB16" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC16" s="44"/>
+      <c r="CD16" s="42"/>
+      <c r="CE16" s="43"/>
+      <c r="CF16" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG16" s="44"/>
+      <c r="CH16" s="42"/>
+      <c r="CI16" s="43"/>
+      <c r="CJ16" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A17" s="31">
         <v>10</v>
       </c>
@@ -3881,19 +4269,19 @@
         <v/>
       </c>
       <c r="G17" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H17" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I17" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J17" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K17" s="33"/>
@@ -3984,7 +4372,7 @@
         <v>10</v>
       </c>
       <c r="BH17" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI17" s="44"/>
@@ -4008,8 +4396,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU17" s="44"/>
+      <c r="BV17" s="42"/>
+      <c r="BW17" s="43"/>
+      <c r="BX17" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY17" s="44"/>
+      <c r="BZ17" s="42"/>
+      <c r="CA17" s="43"/>
+      <c r="CB17" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC17" s="44"/>
+      <c r="CD17" s="42"/>
+      <c r="CE17" s="43"/>
+      <c r="CF17" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG17" s="44"/>
+      <c r="CH17" s="42"/>
+      <c r="CI17" s="43"/>
+      <c r="CJ17" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>11</v>
       </c>
@@ -4022,19 +4438,19 @@
         <v/>
       </c>
       <c r="G18" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H18" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I18" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J18" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K18" s="33"/>
@@ -4125,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="BH18" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI18" s="44"/>
@@ -4149,8 +4565,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU18" s="44"/>
+      <c r="BV18" s="42"/>
+      <c r="BW18" s="43"/>
+      <c r="BX18" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY18" s="44"/>
+      <c r="BZ18" s="42"/>
+      <c r="CA18" s="43"/>
+      <c r="CB18" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC18" s="44"/>
+      <c r="CD18" s="42"/>
+      <c r="CE18" s="43"/>
+      <c r="CF18" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG18" s="44"/>
+      <c r="CH18" s="42"/>
+      <c r="CI18" s="43"/>
+      <c r="CJ18" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>12</v>
       </c>
@@ -4163,19 +4607,19 @@
         <v/>
       </c>
       <c r="G19" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H19" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I19" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J19" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K19" s="33"/>
@@ -4266,7 +4710,7 @@
         <v>12</v>
       </c>
       <c r="BH19" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI19" s="44"/>
@@ -4290,8 +4734,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU19" s="44"/>
+      <c r="BV19" s="42"/>
+      <c r="BW19" s="43"/>
+      <c r="BX19" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY19" s="44"/>
+      <c r="BZ19" s="42"/>
+      <c r="CA19" s="43"/>
+      <c r="CB19" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC19" s="44"/>
+      <c r="CD19" s="42"/>
+      <c r="CE19" s="43"/>
+      <c r="CF19" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG19" s="44"/>
+      <c r="CH19" s="42"/>
+      <c r="CI19" s="43"/>
+      <c r="CJ19" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A20" s="31">
         <v>13</v>
       </c>
@@ -4304,19 +4776,19 @@
         <v/>
       </c>
       <c r="G20" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H20" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I20" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J20" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K20" s="33"/>
@@ -4407,7 +4879,7 @@
         <v>13</v>
       </c>
       <c r="BH20" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI20" s="44"/>
@@ -4431,8 +4903,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU20" s="44"/>
+      <c r="BV20" s="42"/>
+      <c r="BW20" s="43"/>
+      <c r="BX20" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY20" s="44"/>
+      <c r="BZ20" s="42"/>
+      <c r="CA20" s="43"/>
+      <c r="CB20" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC20" s="44"/>
+      <c r="CD20" s="42"/>
+      <c r="CE20" s="43"/>
+      <c r="CF20" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG20" s="44"/>
+      <c r="CH20" s="42"/>
+      <c r="CI20" s="43"/>
+      <c r="CJ20" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="21" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A21" s="31">
         <v>14</v>
       </c>
@@ -4445,19 +4945,19 @@
         <v/>
       </c>
       <c r="G21" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H21" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I21" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J21" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K21" s="33"/>
@@ -4548,7 +5048,7 @@
         <v>14</v>
       </c>
       <c r="BH21" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI21" s="44"/>
@@ -4572,8 +5072,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU21" s="44"/>
+      <c r="BV21" s="42"/>
+      <c r="BW21" s="43"/>
+      <c r="BX21" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY21" s="44"/>
+      <c r="BZ21" s="42"/>
+      <c r="CA21" s="43"/>
+      <c r="CB21" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC21" s="44"/>
+      <c r="CD21" s="42"/>
+      <c r="CE21" s="43"/>
+      <c r="CF21" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG21" s="44"/>
+      <c r="CH21" s="42"/>
+      <c r="CI21" s="43"/>
+      <c r="CJ21" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A22" s="31">
         <v>15</v>
       </c>
@@ -4586,19 +5114,19 @@
         <v/>
       </c>
       <c r="G22" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H22" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I22" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J22" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K22" s="33"/>
@@ -4689,7 +5217,7 @@
         <v>15</v>
       </c>
       <c r="BH22" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI22" s="44"/>
@@ -4713,8 +5241,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU22" s="44"/>
+      <c r="BV22" s="42"/>
+      <c r="BW22" s="43"/>
+      <c r="BX22" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY22" s="44"/>
+      <c r="BZ22" s="42"/>
+      <c r="CA22" s="43"/>
+      <c r="CB22" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC22" s="44"/>
+      <c r="CD22" s="42"/>
+      <c r="CE22" s="43"/>
+      <c r="CF22" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG22" s="44"/>
+      <c r="CH22" s="42"/>
+      <c r="CI22" s="43"/>
+      <c r="CJ22" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A23" s="31">
         <v>16</v>
       </c>
@@ -4727,19 +5283,19 @@
         <v/>
       </c>
       <c r="G23" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H23" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I23" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J23" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K23" s="33"/>
@@ -4830,7 +5386,7 @@
         <v>16</v>
       </c>
       <c r="BH23" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI23" s="44"/>
@@ -4854,8 +5410,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU23" s="44"/>
+      <c r="BV23" s="42"/>
+      <c r="BW23" s="43"/>
+      <c r="BX23" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY23" s="44"/>
+      <c r="BZ23" s="42"/>
+      <c r="CA23" s="43"/>
+      <c r="CB23" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC23" s="44"/>
+      <c r="CD23" s="42"/>
+      <c r="CE23" s="43"/>
+      <c r="CF23" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG23" s="44"/>
+      <c r="CH23" s="42"/>
+      <c r="CI23" s="43"/>
+      <c r="CJ23" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A24" s="31">
         <v>17</v>
       </c>
@@ -4868,19 +5452,19 @@
         <v/>
       </c>
       <c r="G24" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H24" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I24" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J24" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K24" s="33"/>
@@ -4971,7 +5555,7 @@
         <v>17</v>
       </c>
       <c r="BH24" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI24" s="44"/>
@@ -4995,8 +5579,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU24" s="44"/>
+      <c r="BV24" s="42"/>
+      <c r="BW24" s="43"/>
+      <c r="BX24" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY24" s="44"/>
+      <c r="BZ24" s="42"/>
+      <c r="CA24" s="43"/>
+      <c r="CB24" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC24" s="44"/>
+      <c r="CD24" s="42"/>
+      <c r="CE24" s="43"/>
+      <c r="CF24" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG24" s="44"/>
+      <c r="CH24" s="42"/>
+      <c r="CI24" s="43"/>
+      <c r="CJ24" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="25" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A25" s="31">
         <v>18</v>
       </c>
@@ -5009,19 +5621,19 @@
         <v/>
       </c>
       <c r="G25" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H25" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I25" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J25" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K25" s="33"/>
@@ -5112,7 +5724,7 @@
         <v>18</v>
       </c>
       <c r="BH25" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI25" s="44"/>
@@ -5136,8 +5748,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU25" s="44"/>
+      <c r="BV25" s="42"/>
+      <c r="BW25" s="43"/>
+      <c r="BX25" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY25" s="44"/>
+      <c r="BZ25" s="42"/>
+      <c r="CA25" s="43"/>
+      <c r="CB25" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC25" s="44"/>
+      <c r="CD25" s="42"/>
+      <c r="CE25" s="43"/>
+      <c r="CF25" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG25" s="44"/>
+      <c r="CH25" s="42"/>
+      <c r="CI25" s="43"/>
+      <c r="CJ25" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A26" s="31">
         <v>19</v>
       </c>
@@ -5150,19 +5790,19 @@
         <v/>
       </c>
       <c r="G26" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H26" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I26" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J26" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K26" s="33"/>
@@ -5253,7 +5893,7 @@
         <v>19</v>
       </c>
       <c r="BH26" s="46" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI26" s="44"/>
@@ -5277,8 +5917,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU26" s="44"/>
+      <c r="BV26" s="42"/>
+      <c r="BW26" s="43"/>
+      <c r="BX26" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY26" s="44"/>
+      <c r="BZ26" s="42"/>
+      <c r="CA26" s="43"/>
+      <c r="CB26" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC26" s="44"/>
+      <c r="CD26" s="42"/>
+      <c r="CE26" s="43"/>
+      <c r="CF26" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG26" s="44"/>
+      <c r="CH26" s="42"/>
+      <c r="CI26" s="43"/>
+      <c r="CJ26" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="27" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A27" s="31">
         <v>20</v>
       </c>
@@ -5291,19 +5959,19 @@
         <v/>
       </c>
       <c r="G27" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H27" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I27" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J27" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K27" s="33"/>
@@ -5394,7 +6062,7 @@
         <v>20</v>
       </c>
       <c r="BH27" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI27" s="44"/>
@@ -5418,8 +6086,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU27" s="44"/>
+      <c r="BV27" s="42"/>
+      <c r="BW27" s="43"/>
+      <c r="BX27" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY27" s="44"/>
+      <c r="BZ27" s="42"/>
+      <c r="CA27" s="43"/>
+      <c r="CB27" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC27" s="44"/>
+      <c r="CD27" s="42"/>
+      <c r="CE27" s="43"/>
+      <c r="CF27" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG27" s="44"/>
+      <c r="CH27" s="42"/>
+      <c r="CI27" s="43"/>
+      <c r="CJ27" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A28" s="31">
         <v>21</v>
       </c>
@@ -5432,19 +6128,19 @@
         <v/>
       </c>
       <c r="G28" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H28" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I28" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J28" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K28" s="33"/>
@@ -5535,7 +6231,7 @@
         <v>21</v>
       </c>
       <c r="BH28" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI28" s="44"/>
@@ -5559,8 +6255,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU28" s="44"/>
+      <c r="BV28" s="42"/>
+      <c r="BW28" s="43"/>
+      <c r="BX28" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY28" s="44"/>
+      <c r="BZ28" s="42"/>
+      <c r="CA28" s="43"/>
+      <c r="CB28" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC28" s="44"/>
+      <c r="CD28" s="42"/>
+      <c r="CE28" s="43"/>
+      <c r="CF28" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG28" s="44"/>
+      <c r="CH28" s="42"/>
+      <c r="CI28" s="43"/>
+      <c r="CJ28" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A29" s="31">
         <v>22</v>
       </c>
@@ -5573,19 +6297,19 @@
         <v/>
       </c>
       <c r="G29" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H29" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I29" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J29" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K29" s="33"/>
@@ -5676,7 +6400,7 @@
         <v>22</v>
       </c>
       <c r="BH29" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI29" s="44"/>
@@ -5700,8 +6424,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU29" s="44"/>
+      <c r="BV29" s="42"/>
+      <c r="BW29" s="43"/>
+      <c r="BX29" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY29" s="44"/>
+      <c r="BZ29" s="42"/>
+      <c r="CA29" s="43"/>
+      <c r="CB29" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC29" s="44"/>
+      <c r="CD29" s="42"/>
+      <c r="CE29" s="43"/>
+      <c r="CF29" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG29" s="44"/>
+      <c r="CH29" s="42"/>
+      <c r="CI29" s="43"/>
+      <c r="CJ29" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="30" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A30" s="31">
         <v>23</v>
       </c>
@@ -5714,19 +6466,19 @@
         <v/>
       </c>
       <c r="G30" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H30" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I30" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J30" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K30" s="33"/>
@@ -5817,7 +6569,7 @@
         <v>23</v>
       </c>
       <c r="BH30" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI30" s="44"/>
@@ -5841,8 +6593,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU30" s="44"/>
+      <c r="BV30" s="42"/>
+      <c r="BW30" s="43"/>
+      <c r="BX30" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY30" s="44"/>
+      <c r="BZ30" s="42"/>
+      <c r="CA30" s="43"/>
+      <c r="CB30" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC30" s="44"/>
+      <c r="CD30" s="42"/>
+      <c r="CE30" s="43"/>
+      <c r="CF30" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG30" s="44"/>
+      <c r="CH30" s="42"/>
+      <c r="CI30" s="43"/>
+      <c r="CJ30" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="31" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>24</v>
       </c>
@@ -5855,19 +6635,19 @@
         <v/>
       </c>
       <c r="G31" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H31" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I31" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J31" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K31" s="33"/>
@@ -5958,7 +6738,7 @@
         <v>24</v>
       </c>
       <c r="BH31" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI31" s="44"/>
@@ -5982,8 +6762,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU31" s="44"/>
+      <c r="BV31" s="42"/>
+      <c r="BW31" s="43"/>
+      <c r="BX31" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY31" s="44"/>
+      <c r="BZ31" s="42"/>
+      <c r="CA31" s="43"/>
+      <c r="CB31" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC31" s="44"/>
+      <c r="CD31" s="42"/>
+      <c r="CE31" s="43"/>
+      <c r="CF31" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG31" s="44"/>
+      <c r="CH31" s="42"/>
+      <c r="CI31" s="43"/>
+      <c r="CJ31" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A32" s="31">
         <v>25</v>
       </c>
@@ -5996,19 +6804,19 @@
         <v/>
       </c>
       <c r="G32" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H32" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I32" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J32" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K32" s="33"/>
@@ -6099,7 +6907,7 @@
         <v>25</v>
       </c>
       <c r="BH32" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI32" s="44"/>
@@ -6123,8 +6931,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU32" s="44"/>
+      <c r="BV32" s="42"/>
+      <c r="BW32" s="43"/>
+      <c r="BX32" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY32" s="44"/>
+      <c r="BZ32" s="42"/>
+      <c r="CA32" s="43"/>
+      <c r="CB32" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC32" s="44"/>
+      <c r="CD32" s="42"/>
+      <c r="CE32" s="43"/>
+      <c r="CF32" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG32" s="44"/>
+      <c r="CH32" s="42"/>
+      <c r="CI32" s="43"/>
+      <c r="CJ32" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="33" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A33" s="31">
         <v>26</v>
       </c>
@@ -6137,19 +6973,19 @@
         <v/>
       </c>
       <c r="G33" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H33" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I33" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J33" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K33" s="33"/>
@@ -6240,7 +7076,7 @@
         <v>26</v>
       </c>
       <c r="BH33" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI33" s="44"/>
@@ -6264,8 +7100,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU33" s="44"/>
+      <c r="BV33" s="42"/>
+      <c r="BW33" s="43"/>
+      <c r="BX33" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY33" s="44"/>
+      <c r="BZ33" s="42"/>
+      <c r="CA33" s="43"/>
+      <c r="CB33" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC33" s="44"/>
+      <c r="CD33" s="42"/>
+      <c r="CE33" s="43"/>
+      <c r="CF33" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG33" s="44"/>
+      <c r="CH33" s="42"/>
+      <c r="CI33" s="43"/>
+      <c r="CJ33" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="34" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A34" s="31">
         <v>27</v>
       </c>
@@ -6278,19 +7142,19 @@
         <v/>
       </c>
       <c r="G34" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H34" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I34" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J34" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K34" s="33"/>
@@ -6381,7 +7245,7 @@
         <v>27</v>
       </c>
       <c r="BH34" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI34" s="44"/>
@@ -6405,8 +7269,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU34" s="44"/>
+      <c r="BV34" s="42"/>
+      <c r="BW34" s="43"/>
+      <c r="BX34" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY34" s="44"/>
+      <c r="BZ34" s="42"/>
+      <c r="CA34" s="43"/>
+      <c r="CB34" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC34" s="44"/>
+      <c r="CD34" s="42"/>
+      <c r="CE34" s="43"/>
+      <c r="CF34" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG34" s="44"/>
+      <c r="CH34" s="42"/>
+      <c r="CI34" s="43"/>
+      <c r="CJ34" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="35" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A35" s="31">
         <v>28</v>
       </c>
@@ -6419,19 +7311,19 @@
         <v/>
       </c>
       <c r="G35" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H35" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I35" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J35" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K35" s="33"/>
@@ -6522,7 +7414,7 @@
         <v>28</v>
       </c>
       <c r="BH35" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI35" s="44"/>
@@ -6546,8 +7438,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU35" s="44"/>
+      <c r="BV35" s="42"/>
+      <c r="BW35" s="43"/>
+      <c r="BX35" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY35" s="44"/>
+      <c r="BZ35" s="42"/>
+      <c r="CA35" s="43"/>
+      <c r="CB35" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC35" s="44"/>
+      <c r="CD35" s="42"/>
+      <c r="CE35" s="43"/>
+      <c r="CF35" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG35" s="44"/>
+      <c r="CH35" s="42"/>
+      <c r="CI35" s="43"/>
+      <c r="CJ35" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="36" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A36" s="31">
         <v>29</v>
       </c>
@@ -6560,19 +7480,19 @@
         <v/>
       </c>
       <c r="G36" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H36" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I36" s="35" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J36" s="37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K36" s="33"/>
@@ -6663,7 +7583,7 @@
         <v>29</v>
       </c>
       <c r="BH36" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI36" s="44"/>
@@ -6687,8 +7607,36 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU36" s="44"/>
+      <c r="BV36" s="42"/>
+      <c r="BW36" s="43"/>
+      <c r="BX36" s="45" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY36" s="44"/>
+      <c r="BZ36" s="42"/>
+      <c r="CA36" s="43"/>
+      <c r="CB36" s="45" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC36" s="44"/>
+      <c r="CD36" s="42"/>
+      <c r="CE36" s="43"/>
+      <c r="CF36" s="45" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG36" s="44"/>
+      <c r="CH36" s="42"/>
+      <c r="CI36" s="43"/>
+      <c r="CJ36" s="45" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="37" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>30</v>
       </c>
@@ -6701,19 +7649,19 @@
         <v/>
       </c>
       <c r="G37" s="50" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H37" s="50" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I37" s="51" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J37" s="53" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K37" s="49"/>
@@ -6804,7 +7752,7 @@
         <v>30</v>
       </c>
       <c r="BH37" s="48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BI37" s="60"/>
@@ -6828,1495 +7776,1843 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
+      <c r="BU37" s="60"/>
+      <c r="BV37" s="58"/>
+      <c r="BW37" s="59"/>
+      <c r="BX37" s="61" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BY37" s="60"/>
+      <c r="BZ37" s="58"/>
+      <c r="CA37" s="59"/>
+      <c r="CB37" s="61" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="CC37" s="60"/>
+      <c r="CD37" s="58"/>
+      <c r="CE37" s="59"/>
+      <c r="CF37" s="61" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG37" s="60"/>
+      <c r="CH37" s="58"/>
+      <c r="CI37" s="59"/>
+      <c r="CJ37" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
     </row>
-    <row r="38" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A38" s="91" t="s">
+    <row r="38" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A38" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="92"/>
+      <c r="B38" s="89"/>
       <c r="C38" s="62" t="str">
-        <f t="shared" ref="C38:AY38" si="23">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
+        <f t="shared" ref="C38:AY38" si="27">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
       </c>
       <c r="D38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="E38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="F38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="G38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="H38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="I38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="J38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="L38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="R38" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="S38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="U38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="V38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="W38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="X38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Y38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Z38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AA38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AB38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AC38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD38" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AE38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AF38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AG38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AH38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AI38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AJ38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AK38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AL38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AM38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AN38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AO38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AP38" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AQ38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AR38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AS38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AT38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AU38" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AV38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AW38" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AX38" s="65" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AY38" s="63" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AZ38" s="63" t="str">
-        <f t="shared" ref="AZ38:BF38" si="24">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ38:BF38" si="28">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA38" s="64" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BB38" s="66" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BC38" s="67" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BD38" s="68" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BE38" s="69" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BF38" s="70" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="BG38" s="91" t="s">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BG38" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="BH38" s="92"/>
+      <c r="BH38" s="89"/>
       <c r="BI38" s="62" t="str">
-        <f t="shared" ref="BI38:BT38" si="25">IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
+        <f t="shared" ref="BI38:BT38" si="29">IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ38" s="63" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BK38" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BL38" s="65" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BM38" s="62" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BN38" s="63" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BO38" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BP38" s="65" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BQ38" s="62" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BR38" s="63" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BS38" s="64" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BT38" s="65" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="BU38" s="62" t="str">
+        <f t="shared" ref="BU38:CJ38" si="30">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV38" s="63" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BW38" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BX38" s="65" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BY38" s="62" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BZ38" s="63" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CA38" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CB38" s="65" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CC38" s="62" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CD38" s="63" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CE38" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CF38" s="65" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CG38" s="62" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CH38" s="63" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CI38" s="64" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="CJ38" s="65" t="str">
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A39" s="93" t="s">
+    <row r="39" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A39" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="94"/>
+      <c r="B39" s="91"/>
       <c r="C39" s="62" t="str">
-        <f t="shared" ref="C39:AY39" si="26">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
+        <f t="shared" ref="C39:AY39" si="31">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
         <v/>
       </c>
       <c r="D39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="E39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="F39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="G39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="H39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="I39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="P39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Q39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="R39" s="66" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="S39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="T39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="U39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="V39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="W39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="X39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Y39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Z39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AA39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AB39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AC39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AD39" s="66" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AE39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AG39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AH39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AI39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AJ39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AK39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AM39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AN39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AO39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AP39" s="66" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AQ39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AR39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AS39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AT39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AU39" s="62" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AV39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AW39" s="64" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AX39" s="65" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AY39" s="63" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AZ39" s="63" t="str">
-        <f t="shared" ref="AZ39:BF39" si="27">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ39:BF39" si="32">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA39" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BB39" s="66" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BC39" s="67" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BD39" s="68" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BE39" s="69" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF39" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BG39" s="93" t="s">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BG39" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="BH39" s="94"/>
+      <c r="BH39" s="91"/>
       <c r="BI39" s="62" t="str">
-        <f t="shared" ref="BI39:BT39" si="28">IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
+        <f t="shared" ref="BI39:BT39" si="33">IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ39" s="63" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BK39" s="64" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BL39" s="65" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BM39" s="62" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BN39" s="63" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BO39" s="64" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BP39" s="65" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BQ39" s="62" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BR39" s="63" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BS39" s="64" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BT39" s="65" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BU39" s="62" t="str">
+        <f t="shared" ref="BU39:CJ39" si="34">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV39" s="63" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BW39" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BX39" s="65" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BY39" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BZ39" s="63" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CA39" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CB39" s="65" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CC39" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CD39" s="63" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CE39" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CF39" s="65" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CG39" s="62" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CH39" s="63" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CI39" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="CJ39" s="65" t="str">
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A40" s="93" t="s">
+    <row r="40" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A40" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="94"/>
+      <c r="B40" s="91"/>
       <c r="C40" s="62" t="str">
-        <f t="shared" ref="C40:AY40" si="29">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
+        <f t="shared" ref="C40:AY40" si="35">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
         <v/>
       </c>
       <c r="D40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="E40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="F40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="H40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="J40" s="66" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="L40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R40" s="66" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="T40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="U40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="W40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="X40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Y40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Z40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AB40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AC40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AD40" s="66" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AE40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AF40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AG40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AH40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AI40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AJ40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AK40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AL40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AM40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AN40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AO40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AP40" s="66" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AQ40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AR40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AS40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AT40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AU40" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AV40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AW40" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AX40" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AY40" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AZ40" s="63" t="str">
-        <f t="shared" ref="AZ40:BF40" si="30">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ40:BF40" si="36">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA40" s="64" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BB40" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BC40" s="67" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BD40" s="68" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BE40" s="69" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BF40" s="70" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="BG40" s="93" t="s">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="BG40" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="BH40" s="94"/>
+      <c r="BH40" s="91"/>
       <c r="BI40" s="62" t="str">
-        <f t="shared" ref="BI40:BT40" si="31">IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
+        <f t="shared" ref="BI40:BT40" si="37">IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ40" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BK40" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BL40" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BM40" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BN40" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BO40" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BP40" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BQ40" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BR40" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BS40" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BT40" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BU40" s="62" t="str">
+        <f t="shared" ref="BU40:CJ40" si="38">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV40" s="63" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BW40" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BX40" s="65" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BY40" s="62" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BZ40" s="63" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CA40" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CB40" s="65" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CC40" s="62" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CD40" s="63" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CE40" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CF40" s="65" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CG40" s="62" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CH40" s="63" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CI40" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="CJ40" s="65" t="str">
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A41" s="93" t="s">
+    <row r="41" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A41" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="94"/>
+      <c r="B41" s="91"/>
       <c r="C41" s="62" t="str">
-        <f t="shared" ref="C41:AY41" si="32">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
+        <f t="shared" ref="C41:AY41" si="39">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
         <v/>
       </c>
       <c r="D41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="E41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="F41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="G41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="H41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="I41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="J41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="L41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="R41" s="66" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="S41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="T41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="U41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="V41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="W41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="X41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Y41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AA41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AB41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AC41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD41" s="66" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AE41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AF41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AG41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AH41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AI41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AJ41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AK41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AL41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AM41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AN41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AO41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AP41" s="66" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AQ41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AR41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AS41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AT41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AU41" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AV41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AW41" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AX41" s="65" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AY41" s="63" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AZ41" s="63" t="str">
-        <f t="shared" ref="AZ41:BF41" si="33">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ41:BF41" si="40">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA41" s="64" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BB41" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BC41" s="67" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BD41" s="68" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BE41" s="69" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BF41" s="70" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BG41" s="93" t="s">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BG41" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="BH41" s="94"/>
+      <c r="BH41" s="91"/>
       <c r="BI41" s="62" t="str">
-        <f t="shared" ref="BI41:BT41" si="34">IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
+        <f t="shared" ref="BI41:BT41" si="41">IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ41" s="63" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BK41" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BL41" s="65" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BM41" s="62" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BN41" s="63" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BO41" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BP41" s="65" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BQ41" s="62" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BR41" s="63" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BS41" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BT41" s="65" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="BU41" s="62" t="str">
+        <f t="shared" ref="BU41:CJ41" si="42">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV41" s="63" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BW41" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BX41" s="65" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BY41" s="62" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BZ41" s="63" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CA41" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CB41" s="65" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CC41" s="62" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CD41" s="63" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CE41" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CF41" s="65" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CG41" s="62" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CH41" s="63" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CI41" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CJ41" s="65" t="str">
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:72" x14ac:dyDescent="0.3">
-      <c r="A42" s="95" t="s">
+    <row r="42" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A42" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="96"/>
+      <c r="B42" s="79"/>
       <c r="C42" s="2" t="str">
-        <f t="shared" ref="C42:AY42" si="35">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
+        <f t="shared" ref="C42:AY42" si="43">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
         <v/>
       </c>
       <c r="D42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="E42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="F42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="G42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="H42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="I42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="J42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="L42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R42" s="6" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="S42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="T42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="U42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="V42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="W42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="X42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Y42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Z42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AA42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AB42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AC42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AD42" s="6" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AE42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AF42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AG42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AI42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AJ42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AK42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AL42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AM42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AN42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AO42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AP42" s="6" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AQ42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AR42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AS42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AT42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AU42" s="2" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AV42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AW42" s="4" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AX42" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AY42" s="3" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AZ42" s="3" t="str">
-        <f t="shared" ref="AZ42:BF42" si="36">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
+        <f t="shared" ref="AZ42:BF42" si="44">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
         <v/>
       </c>
       <c r="BA42" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BB42" s="6" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BC42" s="7" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BD42" s="8" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BE42" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BF42" s="10" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="BG42" s="95" t="s">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="BG42" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="BH42" s="96"/>
+      <c r="BH42" s="79"/>
       <c r="BI42" s="2" t="str">
-        <f t="shared" ref="BI42:BT42" si="37">IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
+        <f t="shared" ref="BI42:BT42" si="45">IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
         <v/>
       </c>
       <c r="BJ42" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BK42" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BL42" s="5" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BM42" s="2" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BN42" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BO42" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BP42" s="5" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BQ42" s="2" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BR42" s="3" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BS42" s="4" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BT42" s="5" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="BU42" s="2" t="str">
+        <f t="shared" ref="BU42:CJ42" si="46">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
+        <v/>
+      </c>
+      <c r="BV42" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="BW42" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="BX42" s="5" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="BY42" s="2" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="BZ42" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CA42" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CB42" s="5" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CC42" s="2" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CD42" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CE42" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CF42" s="5" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CG42" s="2" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CH42" s="3" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CI42" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CJ42" s="5" t="str">
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:82" x14ac:dyDescent="0.3">
-      <c r="A50" s="102" t="s">
+      <c r="A50" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B50" s="103"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="103"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="103"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="103"/>
-      <c r="J50" s="103"/>
-      <c r="K50" s="103"/>
-      <c r="L50" s="103"/>
-      <c r="M50" s="103"/>
-      <c r="N50" s="103"/>
-      <c r="O50" s="103"/>
-      <c r="P50" s="103"/>
-      <c r="Q50" s="103"/>
-      <c r="R50" s="103"/>
-      <c r="S50" s="102" t="s">
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="77"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="77"/>
+      <c r="M50" s="77"/>
+      <c r="N50" s="77"/>
+      <c r="O50" s="77"/>
+      <c r="P50" s="77"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="77"/>
+      <c r="S50" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="T50" s="102"/>
-      <c r="U50" s="102"/>
-      <c r="V50" s="102"/>
-      <c r="W50" s="102"/>
-      <c r="X50" s="102"/>
-      <c r="Y50" s="102"/>
-      <c r="Z50" s="102"/>
-      <c r="AA50" s="102"/>
-      <c r="AB50" s="102"/>
-      <c r="AC50" s="102"/>
-      <c r="AD50" s="102"/>
-      <c r="AE50" s="102"/>
-      <c r="AF50" s="102"/>
-      <c r="AG50" s="102"/>
-      <c r="AH50" s="102"/>
+      <c r="T50" s="76"/>
+      <c r="U50" s="76"/>
+      <c r="V50" s="76"/>
+      <c r="W50" s="76"/>
+      <c r="X50" s="76"/>
+      <c r="Y50" s="76"/>
+      <c r="Z50" s="76"/>
+      <c r="AA50" s="76"/>
+      <c r="AB50" s="76"/>
+      <c r="AC50" s="76"/>
+      <c r="AD50" s="76"/>
+      <c r="AE50" s="76"/>
+      <c r="AF50" s="76"/>
+      <c r="AG50" s="76"/>
+      <c r="AH50" s="76"/>
       <c r="AI50" s="1"/>
-      <c r="AK50" s="102" t="s">
+      <c r="AK50" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="AL50" s="103"/>
-      <c r="AM50" s="103"/>
-      <c r="AN50" s="103"/>
-      <c r="AO50" s="103"/>
-      <c r="AP50" s="103"/>
-      <c r="AQ50" s="103"/>
-      <c r="AR50" s="103"/>
-      <c r="AS50" s="103"/>
-      <c r="AT50" s="103"/>
-      <c r="AU50" s="103"/>
-      <c r="AV50" s="103"/>
-      <c r="AW50" s="103"/>
-      <c r="AX50" s="103"/>
-      <c r="AY50" s="103"/>
-      <c r="AZ50" s="103"/>
-      <c r="BA50" s="103"/>
-      <c r="BB50" s="103"/>
+      <c r="AL50" s="77"/>
+      <c r="AM50" s="77"/>
+      <c r="AN50" s="77"/>
+      <c r="AO50" s="77"/>
+      <c r="AP50" s="77"/>
+      <c r="AQ50" s="77"/>
+      <c r="AR50" s="77"/>
+      <c r="AS50" s="77"/>
+      <c r="AT50" s="77"/>
+      <c r="AU50" s="77"/>
+      <c r="AV50" s="77"/>
+      <c r="AW50" s="77"/>
+      <c r="AX50" s="77"/>
+      <c r="AY50" s="77"/>
+      <c r="AZ50" s="77"/>
+      <c r="BA50" s="77"/>
+      <c r="BB50" s="77"/>
       <c r="BH50" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="BI50" s="102"/>
-      <c r="BJ50" s="102"/>
+      <c r="BI50" s="76"/>
+      <c r="BJ50" s="76"/>
       <c r="BK50" s="72"/>
       <c r="BL50" s="72"/>
-      <c r="BM50" s="102" t="s">
+      <c r="BM50" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="BN50" s="102"/>
-      <c r="BO50" s="102"/>
-      <c r="BP50" s="102"/>
-      <c r="BQ50" s="102"/>
-      <c r="BR50" s="102"/>
-      <c r="BS50" s="102"/>
-      <c r="BT50" s="102"/>
-      <c r="BU50" s="102"/>
+      <c r="BN50" s="76"/>
+      <c r="BO50" s="76"/>
+      <c r="BP50" s="76"/>
+      <c r="BQ50" s="76"/>
+      <c r="BR50" s="76"/>
+      <c r="BS50" s="76"/>
+      <c r="BT50" s="76"/>
+      <c r="BU50" s="76"/>
       <c r="BV50" s="72"/>
       <c r="BW50" s="72"/>
       <c r="BX50" s="72"/>
@@ -8328,86 +9624,86 @@
       <c r="CD50" s="72"/>
     </row>
     <row r="51" spans="1:82" x14ac:dyDescent="0.3">
-      <c r="A51" s="103" t="s">
+      <c r="A51" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="103"/>
-      <c r="C51" s="103"/>
-      <c r="D51" s="103"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="103"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="103"/>
-      <c r="I51" s="103"/>
-      <c r="J51" s="103"/>
-      <c r="K51" s="103"/>
-      <c r="L51" s="103"/>
-      <c r="M51" s="103"/>
-      <c r="N51" s="103"/>
-      <c r="O51" s="103"/>
-      <c r="P51" s="103"/>
-      <c r="Q51" s="103"/>
-      <c r="R51" s="103"/>
-      <c r="S51" s="103" t="s">
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="77"/>
+      <c r="I51" s="77"/>
+      <c r="J51" s="77"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="77"/>
+      <c r="M51" s="77"/>
+      <c r="N51" s="77"/>
+      <c r="O51" s="77"/>
+      <c r="P51" s="77"/>
+      <c r="Q51" s="77"/>
+      <c r="R51" s="77"/>
+      <c r="S51" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="T51" s="103"/>
-      <c r="U51" s="103"/>
-      <c r="V51" s="103"/>
-      <c r="W51" s="103"/>
-      <c r="X51" s="103"/>
-      <c r="Y51" s="103"/>
-      <c r="Z51" s="103"/>
-      <c r="AA51" s="103"/>
-      <c r="AB51" s="103"/>
-      <c r="AC51" s="103"/>
-      <c r="AD51" s="103"/>
-      <c r="AE51" s="103"/>
-      <c r="AF51" s="103"/>
-      <c r="AG51" s="103"/>
-      <c r="AH51" s="103"/>
+      <c r="T51" s="77"/>
+      <c r="U51" s="77"/>
+      <c r="V51" s="77"/>
+      <c r="W51" s="77"/>
+      <c r="X51" s="77"/>
+      <c r="Y51" s="77"/>
+      <c r="Z51" s="77"/>
+      <c r="AA51" s="77"/>
+      <c r="AB51" s="77"/>
+      <c r="AC51" s="77"/>
+      <c r="AD51" s="77"/>
+      <c r="AE51" s="77"/>
+      <c r="AF51" s="77"/>
+      <c r="AG51" s="77"/>
+      <c r="AH51" s="77"/>
       <c r="AI51" s="1"/>
-      <c r="AK51" s="103" t="s">
+      <c r="AK51" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="AL51" s="103"/>
-      <c r="AM51" s="103"/>
-      <c r="AN51" s="103"/>
-      <c r="AO51" s="103"/>
-      <c r="AP51" s="103"/>
-      <c r="AQ51" s="103"/>
-      <c r="AR51" s="103"/>
-      <c r="AS51" s="103"/>
-      <c r="AT51" s="103"/>
-      <c r="AU51" s="103"/>
-      <c r="AV51" s="103"/>
-      <c r="AW51" s="103"/>
-      <c r="AX51" s="103"/>
-      <c r="AY51" s="103"/>
-      <c r="AZ51" s="103"/>
-      <c r="BA51" s="103"/>
-      <c r="BB51" s="103"/>
+      <c r="AL51" s="77"/>
+      <c r="AM51" s="77"/>
+      <c r="AN51" s="77"/>
+      <c r="AO51" s="77"/>
+      <c r="AP51" s="77"/>
+      <c r="AQ51" s="77"/>
+      <c r="AR51" s="77"/>
+      <c r="AS51" s="77"/>
+      <c r="AT51" s="77"/>
+      <c r="AU51" s="77"/>
+      <c r="AV51" s="77"/>
+      <c r="AW51" s="77"/>
+      <c r="AX51" s="77"/>
+      <c r="AY51" s="77"/>
+      <c r="AZ51" s="77"/>
+      <c r="BA51" s="77"/>
+      <c r="BB51" s="77"/>
       <c r="BE51" t="s">
         <v>36</v>
       </c>
       <c r="BH51" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="BI51" s="103"/>
-      <c r="BJ51" s="103"/>
+      <c r="BI51" s="77"/>
+      <c r="BJ51" s="77"/>
       <c r="BK51" s="72"/>
       <c r="BL51" s="72"/>
-      <c r="BM51" s="103" t="s">
+      <c r="BM51" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="BN51" s="103"/>
-      <c r="BO51" s="103"/>
-      <c r="BP51" s="103"/>
-      <c r="BQ51" s="103"/>
-      <c r="BR51" s="103"/>
-      <c r="BS51" s="103"/>
-      <c r="BT51" s="103"/>
-      <c r="BU51" s="103"/>
+      <c r="BN51" s="77"/>
+      <c r="BO51" s="77"/>
+      <c r="BP51" s="77"/>
+      <c r="BQ51" s="77"/>
+      <c r="BR51" s="77"/>
+      <c r="BS51" s="77"/>
+      <c r="BT51" s="77"/>
+      <c r="BU51" s="77"/>
       <c r="BV51" s="72"/>
       <c r="BW51" s="72"/>
       <c r="BX51" s="72"/>
@@ -8505,26 +9801,25 @@
       <c r="AP54" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="BM50:BU50"/>
-    <mergeCell ref="BM51:BU51"/>
-    <mergeCell ref="A50:R50"/>
-    <mergeCell ref="AK50:BB50"/>
-    <mergeCell ref="A51:R51"/>
-    <mergeCell ref="AK51:BB51"/>
-    <mergeCell ref="S50:AH50"/>
-    <mergeCell ref="S51:AH51"/>
-    <mergeCell ref="BI50:BJ50"/>
-    <mergeCell ref="BI51:BJ51"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
+  <mergeCells count="53">
+    <mergeCell ref="BU6:BX6"/>
+    <mergeCell ref="BY6:CB6"/>
+    <mergeCell ref="CC6:CF6"/>
+    <mergeCell ref="CG6:CJ6"/>
+    <mergeCell ref="BG2:CJ2"/>
+    <mergeCell ref="BG3:CJ3"/>
+    <mergeCell ref="BG4:CJ4"/>
+    <mergeCell ref="BG5:CJ5"/>
+    <mergeCell ref="BI6:BL6"/>
+    <mergeCell ref="BM6:BP6"/>
+    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="BG6:BG7"/>
+    <mergeCell ref="BH6:BH7"/>
+    <mergeCell ref="BG38:BH38"/>
+    <mergeCell ref="BG39:BH39"/>
+    <mergeCell ref="BG40:BH40"/>
+    <mergeCell ref="BG41:BH41"/>
+    <mergeCell ref="BG42:BH42"/>
     <mergeCell ref="A2:BF2"/>
     <mergeCell ref="A3:BF3"/>
     <mergeCell ref="A4:BF4"/>
@@ -8541,28 +9836,45 @@
     <mergeCell ref="AA6:AD6"/>
     <mergeCell ref="AE6:AH6"/>
     <mergeCell ref="W6:Z6"/>
-    <mergeCell ref="BG38:BH38"/>
-    <mergeCell ref="BG39:BH39"/>
-    <mergeCell ref="BG40:BH40"/>
-    <mergeCell ref="BG41:BH41"/>
-    <mergeCell ref="BG42:BH42"/>
-    <mergeCell ref="BI6:BL6"/>
-    <mergeCell ref="BM6:BP6"/>
-    <mergeCell ref="BQ6:BT6"/>
-    <mergeCell ref="BG2:BT2"/>
-    <mergeCell ref="BG3:BT3"/>
-    <mergeCell ref="BG4:BT4"/>
-    <mergeCell ref="BG5:BT5"/>
-    <mergeCell ref="BG6:BG7"/>
-    <mergeCell ref="BH6:BH7"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="BM50:BU50"/>
+    <mergeCell ref="BM51:BU51"/>
+    <mergeCell ref="A50:R50"/>
+    <mergeCell ref="AK50:BB50"/>
+    <mergeCell ref="A51:R51"/>
+    <mergeCell ref="AK51:BB51"/>
+    <mergeCell ref="S50:AH50"/>
+    <mergeCell ref="S51:AH51"/>
+    <mergeCell ref="BI50:BJ50"/>
+    <mergeCell ref="BI51:BJ51"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:BF37">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
+      <formula>1</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI8:BT37">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI8:BT37">
+  <conditionalFormatting sqref="BU8:CB37">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>1</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CC8:CJ37">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>1</formula>
       <formula>50</formula>

--- a/public/templates/cs34.xlsx
+++ b/public/templates/cs34.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4259C62C-171C-4C4C-8776-CB937818F6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBC816F-D6E7-4E9E-BDB9-BCCF0625DAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Central!$A$1:$CJ$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Central!$A$1:$CA$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="40">
   <si>
     <t>Nº</t>
   </si>
@@ -144,13 +147,16 @@
     <t>DPTO. INFORMÁTICA</t>
   </si>
   <si>
-    <t>1 de 1</t>
-  </si>
-  <si>
     <t>1 de 2</t>
   </si>
   <si>
     <t>Cos, Fil y Psi.</t>
+  </si>
+  <si>
+    <t>2 de 2</t>
+  </si>
+  <si>
+    <t>------------------------------------------------</t>
   </si>
 </sst>
 </file>
@@ -163,7 +169,7 @@
     <numFmt numFmtId="166" formatCode="#.00"/>
     <numFmt numFmtId="167" formatCode="%#.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,6 +351,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1261,12 +1273,12 @@
     <xf numFmtId="0" fontId="25" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1430,27 +1442,7 @@
     <cellStyle name="Title" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Warning Text" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1569,7 +1561,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>59</xdr:col>
-      <xdr:colOff>977900</xdr:colOff>
+      <xdr:colOff>882650</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>155575</xdr:rowOff>
     </xdr:to>
@@ -1958,18 +1950,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CJ54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:CD54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" customWidth="1"/>
     <col min="3" max="58" width="4" customWidth="1"/>
-    <col min="59" max="59" width="3.88671875" customWidth="1"/>
-    <col min="60" max="60" width="29.44140625" customWidth="1"/>
-    <col min="61" max="88" width="4.5546875" customWidth="1"/>
+    <col min="59" max="59" width="5.28515625" customWidth="1"/>
+    <col min="60" max="60" width="50" customWidth="1"/>
+    <col min="61" max="72" width="6.5703125" customWidth="1"/>
+    <col min="73" max="75" width="4.7109375" customWidth="1"/>
+    <col min="76" max="81" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A2" s="92" t="s">
         <v>8</v>
       </c>
@@ -2047,24 +2041,8 @@
       <c r="BR2" s="92"/>
       <c r="BS2" s="92"/>
       <c r="BT2" s="92"/>
-      <c r="BU2" s="92"/>
-      <c r="BV2" s="92"/>
-      <c r="BW2" s="92"/>
-      <c r="BX2" s="92"/>
-      <c r="BY2" s="92"/>
-      <c r="BZ2" s="92"/>
-      <c r="CA2" s="92"/>
-      <c r="CB2" s="92"/>
-      <c r="CC2" s="92"/>
-      <c r="CD2" s="92"/>
-      <c r="CE2" s="92"/>
-      <c r="CF2" s="92"/>
-      <c r="CG2" s="92"/>
-      <c r="CH2" s="92"/>
-      <c r="CI2" s="92"/>
-      <c r="CJ2" s="92"/>
     </row>
-    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A3" s="93" t="s">
         <v>9</v>
       </c>
@@ -2142,24 +2120,8 @@
       <c r="BR3" s="93"/>
       <c r="BS3" s="93"/>
       <c r="BT3" s="93"/>
-      <c r="BU3" s="93"/>
-      <c r="BV3" s="93"/>
-      <c r="BW3" s="93"/>
-      <c r="BX3" s="93"/>
-      <c r="BY3" s="93"/>
-      <c r="BZ3" s="93"/>
-      <c r="CA3" s="93"/>
-      <c r="CB3" s="93"/>
-      <c r="CC3" s="93"/>
-      <c r="CD3" s="93"/>
-      <c r="CE3" s="93"/>
-      <c r="CF3" s="93"/>
-      <c r="CG3" s="93"/>
-      <c r="CH3" s="93"/>
-      <c r="CI3" s="93"/>
-      <c r="CJ3" s="93"/>
     </row>
-    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A4" s="94"/>
       <c r="B4" s="94"/>
       <c r="C4" s="94"/>
@@ -2235,24 +2197,8 @@
       <c r="BR4" s="94"/>
       <c r="BS4" s="94"/>
       <c r="BT4" s="94"/>
-      <c r="BU4" s="94"/>
-      <c r="BV4" s="94"/>
-      <c r="BW4" s="94"/>
-      <c r="BX4" s="94"/>
-      <c r="BY4" s="94"/>
-      <c r="BZ4" s="94"/>
-      <c r="CA4" s="94"/>
-      <c r="CB4" s="94"/>
-      <c r="CC4" s="94"/>
-      <c r="CD4" s="94"/>
-      <c r="CE4" s="94"/>
-      <c r="CF4" s="94"/>
-      <c r="CG4" s="94"/>
-      <c r="CH4" s="94"/>
-      <c r="CI4" s="94"/>
-      <c r="CJ4" s="94"/>
     </row>
-    <row r="5" spans="1:88" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="95"/>
       <c r="B5" s="95"/>
       <c r="C5" s="95"/>
@@ -2328,24 +2274,8 @@
       <c r="BR5" s="95"/>
       <c r="BS5" s="95"/>
       <c r="BT5" s="95"/>
-      <c r="BU5" s="95"/>
-      <c r="BV5" s="95"/>
-      <c r="BW5" s="95"/>
-      <c r="BX5" s="95"/>
-      <c r="BY5" s="95"/>
-      <c r="BZ5" s="95"/>
-      <c r="CA5" s="95"/>
-      <c r="CB5" s="95"/>
-      <c r="CC5" s="95"/>
-      <c r="CD5" s="95"/>
-      <c r="CE5" s="95"/>
-      <c r="CF5" s="95"/>
-      <c r="CG5" s="95"/>
-      <c r="CH5" s="95"/>
-      <c r="CI5" s="95"/>
-      <c r="CJ5" s="95"/>
     </row>
-    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A6" s="84" t="s">
         <v>0</v>
       </c>
@@ -2419,7 +2349,7 @@
       <c r="AS6" s="82"/>
       <c r="AT6" s="83"/>
       <c r="AU6" s="80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AV6" s="81"/>
       <c r="AW6" s="82"/>
@@ -2460,24 +2390,8 @@
       <c r="BR6" s="81"/>
       <c r="BS6" s="82"/>
       <c r="BT6" s="83"/>
-      <c r="BU6" s="101"/>
-      <c r="BV6" s="102"/>
-      <c r="BW6" s="102"/>
-      <c r="BX6" s="102"/>
-      <c r="BY6" s="101"/>
-      <c r="BZ6" s="102"/>
-      <c r="CA6" s="102"/>
-      <c r="CB6" s="103"/>
-      <c r="CC6" s="101"/>
-      <c r="CD6" s="102"/>
-      <c r="CE6" s="102"/>
-      <c r="CF6" s="102"/>
-      <c r="CG6" s="101"/>
-      <c r="CH6" s="102"/>
-      <c r="CI6" s="102"/>
-      <c r="CJ6" s="103"/>
     </row>
-    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A7" s="85"/>
       <c r="B7" s="87"/>
       <c r="C7" s="2" t="s">
@@ -2686,56 +2600,8 @@
       <c r="BT7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="BU7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BV7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="BW7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="BX7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="BY7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="BZ7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="CA7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="CB7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="CC7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="CD7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="CE7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="CF7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="CG7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="CH7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="CI7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="CJ7" s="15" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>1</v>
       </c>
@@ -2875,36 +2741,8 @@
         <f t="shared" ref="BT8:BT37" si="17">IF(SUM(BQ8:BS8)=0,"",ROUND(AVERAGE(BQ8:BS8),0))</f>
         <v/>
       </c>
-      <c r="BU8" s="29"/>
-      <c r="BV8" s="27"/>
-      <c r="BW8" s="28"/>
-      <c r="BX8" s="30" t="str">
-        <f t="shared" ref="BX8:BX37" si="18">IF(SUM(BU8:BW8)=0,"",ROUND(AVERAGE(BU8:BW8),0))</f>
-        <v/>
-      </c>
-      <c r="BY8" s="29"/>
-      <c r="BZ8" s="27"/>
-      <c r="CA8" s="28"/>
-      <c r="CB8" s="30" t="str">
-        <f t="shared" ref="CB8:CB37" si="19">IF(SUM(BY8:CA8)=0,"",ROUND(AVERAGE(BY8:CA8),0))</f>
-        <v/>
-      </c>
-      <c r="CC8" s="29"/>
-      <c r="CD8" s="27"/>
-      <c r="CE8" s="28"/>
-      <c r="CF8" s="30" t="str">
-        <f t="shared" ref="CF8:CF37" si="20">IF(SUM(CC8:CE8)=0,"",ROUND(AVERAGE(CC8:CE8),0))</f>
-        <v/>
-      </c>
-      <c r="CG8" s="29"/>
-      <c r="CH8" s="27"/>
-      <c r="CI8" s="28"/>
-      <c r="CJ8" s="30" t="str">
-        <f t="shared" ref="CJ8:CJ37" si="21">IF(SUM(CG8:CI8)=0,"",ROUND(AVERAGE(CG8:CI8),0))</f>
-        <v/>
-      </c>
     </row>
-    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>2</v>
       </c>
@@ -2917,19 +2755,19 @@
         <v/>
       </c>
       <c r="G9" s="34" t="str">
-        <f t="shared" ref="G9:G37" si="22">IF(BQ9="","",BQ9)</f>
+        <f t="shared" ref="G9:G37" si="18">IF(BQ9="","",BQ9)</f>
         <v/>
       </c>
       <c r="H9" s="34" t="str">
-        <f t="shared" ref="H9:H37" si="23">IF(BR9="","",BR9)</f>
+        <f t="shared" ref="H9:H37" si="19">IF(BR9="","",BR9)</f>
         <v/>
       </c>
       <c r="I9" s="35" t="str">
-        <f t="shared" ref="I9:I37" si="24">IF(BS9="","",BS9)</f>
+        <f t="shared" ref="I9:I37" si="20">IF(BS9="","",BS9)</f>
         <v/>
       </c>
       <c r="J9" s="37" t="str">
-        <f t="shared" ref="J9:J37" si="25">IF(BT9="","",BT9)</f>
+        <f t="shared" ref="J9:J37" si="21">IF(BT9="","",BT9)</f>
         <v/>
       </c>
       <c r="K9" s="33"/>
@@ -3020,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="BH9" s="32" t="str">
-        <f t="shared" ref="BH9:BH37" si="26">IF(B9="","",B9)</f>
+        <f t="shared" ref="BH9:BH37" si="22">IF(B9="","",B9)</f>
         <v/>
       </c>
       <c r="BI9" s="44"/>
@@ -3044,36 +2882,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU9" s="44"/>
-      <c r="BV9" s="42"/>
-      <c r="BW9" s="43"/>
-      <c r="BX9" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY9" s="44"/>
-      <c r="BZ9" s="42"/>
-      <c r="CA9" s="43"/>
-      <c r="CB9" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC9" s="44"/>
-      <c r="CD9" s="42"/>
-      <c r="CE9" s="43"/>
-      <c r="CF9" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG9" s="44"/>
-      <c r="CH9" s="42"/>
-      <c r="CI9" s="43"/>
-      <c r="CJ9" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>3</v>
       </c>
@@ -3086,19 +2896,19 @@
         <v/>
       </c>
       <c r="G10" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H10" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I10" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J10" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K10" s="33"/>
@@ -3189,7 +2999,7 @@
         <v>3</v>
       </c>
       <c r="BH10" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI10" s="44"/>
@@ -3213,36 +3023,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU10" s="44"/>
-      <c r="BV10" s="42"/>
-      <c r="BW10" s="43"/>
-      <c r="BX10" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY10" s="44"/>
-      <c r="BZ10" s="42"/>
-      <c r="CA10" s="43"/>
-      <c r="CB10" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC10" s="44"/>
-      <c r="CD10" s="42"/>
-      <c r="CE10" s="43"/>
-      <c r="CF10" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG10" s="44"/>
-      <c r="CH10" s="42"/>
-      <c r="CI10" s="43"/>
-      <c r="CJ10" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>4</v>
       </c>
@@ -3255,19 +3037,19 @@
         <v/>
       </c>
       <c r="G11" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H11" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I11" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J11" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K11" s="33"/>
@@ -3358,7 +3140,7 @@
         <v>4</v>
       </c>
       <c r="BH11" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI11" s="44"/>
@@ -3382,36 +3164,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU11" s="44"/>
-      <c r="BV11" s="42"/>
-      <c r="BW11" s="43"/>
-      <c r="BX11" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY11" s="44"/>
-      <c r="BZ11" s="42"/>
-      <c r="CA11" s="43"/>
-      <c r="CB11" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC11" s="44"/>
-      <c r="CD11" s="42"/>
-      <c r="CE11" s="43"/>
-      <c r="CF11" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG11" s="44"/>
-      <c r="CH11" s="42"/>
-      <c r="CI11" s="43"/>
-      <c r="CJ11" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>5</v>
       </c>
@@ -3424,19 +3178,19 @@
         <v/>
       </c>
       <c r="G12" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H12" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I12" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J12" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K12" s="33"/>
@@ -3527,7 +3281,7 @@
         <v>5</v>
       </c>
       <c r="BH12" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI12" s="44"/>
@@ -3551,36 +3305,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU12" s="44"/>
-      <c r="BV12" s="42"/>
-      <c r="BW12" s="43"/>
-      <c r="BX12" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY12" s="44"/>
-      <c r="BZ12" s="42"/>
-      <c r="CA12" s="43"/>
-      <c r="CB12" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC12" s="44"/>
-      <c r="CD12" s="42"/>
-      <c r="CE12" s="43"/>
-      <c r="CF12" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG12" s="44"/>
-      <c r="CH12" s="42"/>
-      <c r="CI12" s="43"/>
-      <c r="CJ12" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>6</v>
       </c>
@@ -3593,19 +3319,19 @@
         <v/>
       </c>
       <c r="G13" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H13" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I13" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J13" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K13" s="33"/>
@@ -3696,7 +3422,7 @@
         <v>6</v>
       </c>
       <c r="BH13" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI13" s="44"/>
@@ -3720,36 +3446,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU13" s="44"/>
-      <c r="BV13" s="42"/>
-      <c r="BW13" s="43"/>
-      <c r="BX13" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY13" s="44"/>
-      <c r="BZ13" s="42"/>
-      <c r="CA13" s="43"/>
-      <c r="CB13" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC13" s="44"/>
-      <c r="CD13" s="42"/>
-      <c r="CE13" s="43"/>
-      <c r="CF13" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG13" s="44"/>
-      <c r="CH13" s="42"/>
-      <c r="CI13" s="43"/>
-      <c r="CJ13" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>7</v>
       </c>
@@ -3762,19 +3460,19 @@
         <v/>
       </c>
       <c r="G14" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H14" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I14" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J14" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K14" s="33"/>
@@ -3865,7 +3563,7 @@
         <v>7</v>
       </c>
       <c r="BH14" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI14" s="44"/>
@@ -3889,36 +3587,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU14" s="44"/>
-      <c r="BV14" s="42"/>
-      <c r="BW14" s="43"/>
-      <c r="BX14" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY14" s="44"/>
-      <c r="BZ14" s="42"/>
-      <c r="CA14" s="43"/>
-      <c r="CB14" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC14" s="44"/>
-      <c r="CD14" s="42"/>
-      <c r="CE14" s="43"/>
-      <c r="CF14" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG14" s="44"/>
-      <c r="CH14" s="42"/>
-      <c r="CI14" s="43"/>
-      <c r="CJ14" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A15" s="31">
         <v>8</v>
       </c>
@@ -3931,19 +3601,19 @@
         <v/>
       </c>
       <c r="G15" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H15" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I15" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J15" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K15" s="33"/>
@@ -4034,7 +3704,7 @@
         <v>8</v>
       </c>
       <c r="BH15" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI15" s="44"/>
@@ -4058,36 +3728,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU15" s="44"/>
-      <c r="BV15" s="42"/>
-      <c r="BW15" s="43"/>
-      <c r="BX15" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY15" s="44"/>
-      <c r="BZ15" s="42"/>
-      <c r="CA15" s="43"/>
-      <c r="CB15" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC15" s="44"/>
-      <c r="CD15" s="42"/>
-      <c r="CE15" s="43"/>
-      <c r="CF15" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG15" s="44"/>
-      <c r="CH15" s="42"/>
-      <c r="CI15" s="43"/>
-      <c r="CJ15" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>9</v>
       </c>
@@ -4100,19 +3742,19 @@
         <v/>
       </c>
       <c r="G16" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H16" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I16" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J16" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K16" s="33"/>
@@ -4203,7 +3845,7 @@
         <v>9</v>
       </c>
       <c r="BH16" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI16" s="44"/>
@@ -4227,36 +3869,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU16" s="44"/>
-      <c r="BV16" s="42"/>
-      <c r="BW16" s="43"/>
-      <c r="BX16" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY16" s="44"/>
-      <c r="BZ16" s="42"/>
-      <c r="CA16" s="43"/>
-      <c r="CB16" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC16" s="44"/>
-      <c r="CD16" s="42"/>
-      <c r="CE16" s="43"/>
-      <c r="CF16" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG16" s="44"/>
-      <c r="CH16" s="42"/>
-      <c r="CI16" s="43"/>
-      <c r="CJ16" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="17" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A17" s="31">
         <v>10</v>
       </c>
@@ -4269,19 +3883,19 @@
         <v/>
       </c>
       <c r="G17" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H17" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I17" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J17" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K17" s="33"/>
@@ -4372,7 +3986,7 @@
         <v>10</v>
       </c>
       <c r="BH17" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI17" s="44"/>
@@ -4396,36 +4010,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU17" s="44"/>
-      <c r="BV17" s="42"/>
-      <c r="BW17" s="43"/>
-      <c r="BX17" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY17" s="44"/>
-      <c r="BZ17" s="42"/>
-      <c r="CA17" s="43"/>
-      <c r="CB17" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC17" s="44"/>
-      <c r="CD17" s="42"/>
-      <c r="CE17" s="43"/>
-      <c r="CF17" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG17" s="44"/>
-      <c r="CH17" s="42"/>
-      <c r="CI17" s="43"/>
-      <c r="CJ17" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="18" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>11</v>
       </c>
@@ -4438,19 +4024,19 @@
         <v/>
       </c>
       <c r="G18" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H18" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I18" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J18" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K18" s="33"/>
@@ -4541,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="BH18" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI18" s="44"/>
@@ -4565,36 +4151,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU18" s="44"/>
-      <c r="BV18" s="42"/>
-      <c r="BW18" s="43"/>
-      <c r="BX18" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY18" s="44"/>
-      <c r="BZ18" s="42"/>
-      <c r="CA18" s="43"/>
-      <c r="CB18" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC18" s="44"/>
-      <c r="CD18" s="42"/>
-      <c r="CE18" s="43"/>
-      <c r="CF18" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG18" s="44"/>
-      <c r="CH18" s="42"/>
-      <c r="CI18" s="43"/>
-      <c r="CJ18" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="19" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A19" s="31">
         <v>12</v>
       </c>
@@ -4607,19 +4165,19 @@
         <v/>
       </c>
       <c r="G19" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H19" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I19" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J19" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K19" s="33"/>
@@ -4710,7 +4268,7 @@
         <v>12</v>
       </c>
       <c r="BH19" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI19" s="44"/>
@@ -4734,36 +4292,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU19" s="44"/>
-      <c r="BV19" s="42"/>
-      <c r="BW19" s="43"/>
-      <c r="BX19" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY19" s="44"/>
-      <c r="BZ19" s="42"/>
-      <c r="CA19" s="43"/>
-      <c r="CB19" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC19" s="44"/>
-      <c r="CD19" s="42"/>
-      <c r="CE19" s="43"/>
-      <c r="CF19" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG19" s="44"/>
-      <c r="CH19" s="42"/>
-      <c r="CI19" s="43"/>
-      <c r="CJ19" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="20" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A20" s="31">
         <v>13</v>
       </c>
@@ -4776,19 +4306,19 @@
         <v/>
       </c>
       <c r="G20" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H20" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I20" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J20" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K20" s="33"/>
@@ -4879,7 +4409,7 @@
         <v>13</v>
       </c>
       <c r="BH20" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI20" s="44"/>
@@ -4903,36 +4433,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU20" s="44"/>
-      <c r="BV20" s="42"/>
-      <c r="BW20" s="43"/>
-      <c r="BX20" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY20" s="44"/>
-      <c r="BZ20" s="42"/>
-      <c r="CA20" s="43"/>
-      <c r="CB20" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC20" s="44"/>
-      <c r="CD20" s="42"/>
-      <c r="CE20" s="43"/>
-      <c r="CF20" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG20" s="44"/>
-      <c r="CH20" s="42"/>
-      <c r="CI20" s="43"/>
-      <c r="CJ20" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="21" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <v>14</v>
       </c>
@@ -4945,19 +4447,19 @@
         <v/>
       </c>
       <c r="G21" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H21" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I21" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J21" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K21" s="33"/>
@@ -5048,7 +4550,7 @@
         <v>14</v>
       </c>
       <c r="BH21" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI21" s="44"/>
@@ -5072,36 +4574,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU21" s="44"/>
-      <c r="BV21" s="42"/>
-      <c r="BW21" s="43"/>
-      <c r="BX21" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY21" s="44"/>
-      <c r="BZ21" s="42"/>
-      <c r="CA21" s="43"/>
-      <c r="CB21" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC21" s="44"/>
-      <c r="CD21" s="42"/>
-      <c r="CE21" s="43"/>
-      <c r="CF21" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG21" s="44"/>
-      <c r="CH21" s="42"/>
-      <c r="CI21" s="43"/>
-      <c r="CJ21" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="22" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A22" s="31">
         <v>15</v>
       </c>
@@ -5114,19 +4588,19 @@
         <v/>
       </c>
       <c r="G22" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H22" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I22" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J22" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K22" s="33"/>
@@ -5217,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="BH22" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI22" s="44"/>
@@ -5241,36 +4715,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU22" s="44"/>
-      <c r="BV22" s="42"/>
-      <c r="BW22" s="43"/>
-      <c r="BX22" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY22" s="44"/>
-      <c r="BZ22" s="42"/>
-      <c r="CA22" s="43"/>
-      <c r="CB22" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC22" s="44"/>
-      <c r="CD22" s="42"/>
-      <c r="CE22" s="43"/>
-      <c r="CF22" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG22" s="44"/>
-      <c r="CH22" s="42"/>
-      <c r="CI22" s="43"/>
-      <c r="CJ22" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="23" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>16</v>
       </c>
@@ -5283,19 +4729,19 @@
         <v/>
       </c>
       <c r="G23" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H23" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I23" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J23" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K23" s="33"/>
@@ -5386,7 +4832,7 @@
         <v>16</v>
       </c>
       <c r="BH23" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI23" s="44"/>
@@ -5410,36 +4856,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU23" s="44"/>
-      <c r="BV23" s="42"/>
-      <c r="BW23" s="43"/>
-      <c r="BX23" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY23" s="44"/>
-      <c r="BZ23" s="42"/>
-      <c r="CA23" s="43"/>
-      <c r="CB23" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC23" s="44"/>
-      <c r="CD23" s="42"/>
-      <c r="CE23" s="43"/>
-      <c r="CF23" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG23" s="44"/>
-      <c r="CH23" s="42"/>
-      <c r="CI23" s="43"/>
-      <c r="CJ23" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="24" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <v>17</v>
       </c>
@@ -5452,19 +4870,19 @@
         <v/>
       </c>
       <c r="G24" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H24" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I24" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J24" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K24" s="33"/>
@@ -5555,7 +4973,7 @@
         <v>17</v>
       </c>
       <c r="BH24" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI24" s="44"/>
@@ -5579,36 +4997,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU24" s="44"/>
-      <c r="BV24" s="42"/>
-      <c r="BW24" s="43"/>
-      <c r="BX24" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY24" s="44"/>
-      <c r="BZ24" s="42"/>
-      <c r="CA24" s="43"/>
-      <c r="CB24" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC24" s="44"/>
-      <c r="CD24" s="42"/>
-      <c r="CE24" s="43"/>
-      <c r="CF24" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG24" s="44"/>
-      <c r="CH24" s="42"/>
-      <c r="CI24" s="43"/>
-      <c r="CJ24" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="25" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <v>18</v>
       </c>
@@ -5621,19 +5011,19 @@
         <v/>
       </c>
       <c r="G25" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H25" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I25" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J25" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K25" s="33"/>
@@ -5724,7 +5114,7 @@
         <v>18</v>
       </c>
       <c r="BH25" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI25" s="44"/>
@@ -5748,36 +5138,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU25" s="44"/>
-      <c r="BV25" s="42"/>
-      <c r="BW25" s="43"/>
-      <c r="BX25" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY25" s="44"/>
-      <c r="BZ25" s="42"/>
-      <c r="CA25" s="43"/>
-      <c r="CB25" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC25" s="44"/>
-      <c r="CD25" s="42"/>
-      <c r="CE25" s="43"/>
-      <c r="CF25" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG25" s="44"/>
-      <c r="CH25" s="42"/>
-      <c r="CI25" s="43"/>
-      <c r="CJ25" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="26" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <v>19</v>
       </c>
@@ -5790,19 +5152,19 @@
         <v/>
       </c>
       <c r="G26" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H26" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I26" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J26" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K26" s="33"/>
@@ -5893,7 +5255,7 @@
         <v>19</v>
       </c>
       <c r="BH26" s="46" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI26" s="44"/>
@@ -5917,36 +5279,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU26" s="44"/>
-      <c r="BV26" s="42"/>
-      <c r="BW26" s="43"/>
-      <c r="BX26" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY26" s="44"/>
-      <c r="BZ26" s="42"/>
-      <c r="CA26" s="43"/>
-      <c r="CB26" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC26" s="44"/>
-      <c r="CD26" s="42"/>
-      <c r="CE26" s="43"/>
-      <c r="CF26" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG26" s="44"/>
-      <c r="CH26" s="42"/>
-      <c r="CI26" s="43"/>
-      <c r="CJ26" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="27" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>20</v>
       </c>
@@ -5959,19 +5293,19 @@
         <v/>
       </c>
       <c r="G27" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H27" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I27" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J27" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K27" s="33"/>
@@ -6062,7 +5396,7 @@
         <v>20</v>
       </c>
       <c r="BH27" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI27" s="44"/>
@@ -6086,36 +5420,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU27" s="44"/>
-      <c r="BV27" s="42"/>
-      <c r="BW27" s="43"/>
-      <c r="BX27" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY27" s="44"/>
-      <c r="BZ27" s="42"/>
-      <c r="CA27" s="43"/>
-      <c r="CB27" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC27" s="44"/>
-      <c r="CD27" s="42"/>
-      <c r="CE27" s="43"/>
-      <c r="CF27" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG27" s="44"/>
-      <c r="CH27" s="42"/>
-      <c r="CI27" s="43"/>
-      <c r="CJ27" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="28" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>21</v>
       </c>
@@ -6128,19 +5434,19 @@
         <v/>
       </c>
       <c r="G28" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H28" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I28" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J28" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K28" s="33"/>
@@ -6231,7 +5537,7 @@
         <v>21</v>
       </c>
       <c r="BH28" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI28" s="44"/>
@@ -6255,36 +5561,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU28" s="44"/>
-      <c r="BV28" s="42"/>
-      <c r="BW28" s="43"/>
-      <c r="BX28" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY28" s="44"/>
-      <c r="BZ28" s="42"/>
-      <c r="CA28" s="43"/>
-      <c r="CB28" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC28" s="44"/>
-      <c r="CD28" s="42"/>
-      <c r="CE28" s="43"/>
-      <c r="CF28" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG28" s="44"/>
-      <c r="CH28" s="42"/>
-      <c r="CI28" s="43"/>
-      <c r="CJ28" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="29" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <v>22</v>
       </c>
@@ -6297,19 +5575,19 @@
         <v/>
       </c>
       <c r="G29" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H29" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I29" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J29" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K29" s="33"/>
@@ -6400,7 +5678,7 @@
         <v>22</v>
       </c>
       <c r="BH29" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI29" s="44"/>
@@ -6424,36 +5702,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU29" s="44"/>
-      <c r="BV29" s="42"/>
-      <c r="BW29" s="43"/>
-      <c r="BX29" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY29" s="44"/>
-      <c r="BZ29" s="42"/>
-      <c r="CA29" s="43"/>
-      <c r="CB29" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC29" s="44"/>
-      <c r="CD29" s="42"/>
-      <c r="CE29" s="43"/>
-      <c r="CF29" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG29" s="44"/>
-      <c r="CH29" s="42"/>
-      <c r="CI29" s="43"/>
-      <c r="CJ29" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="30" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <v>23</v>
       </c>
@@ -6466,19 +5716,19 @@
         <v/>
       </c>
       <c r="G30" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H30" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I30" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J30" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K30" s="33"/>
@@ -6569,7 +5819,7 @@
         <v>23</v>
       </c>
       <c r="BH30" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI30" s="44"/>
@@ -6593,36 +5843,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU30" s="44"/>
-      <c r="BV30" s="42"/>
-      <c r="BW30" s="43"/>
-      <c r="BX30" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY30" s="44"/>
-      <c r="BZ30" s="42"/>
-      <c r="CA30" s="43"/>
-      <c r="CB30" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC30" s="44"/>
-      <c r="CD30" s="42"/>
-      <c r="CE30" s="43"/>
-      <c r="CF30" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG30" s="44"/>
-      <c r="CH30" s="42"/>
-      <c r="CI30" s="43"/>
-      <c r="CJ30" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="31" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>24</v>
       </c>
@@ -6635,19 +5857,19 @@
         <v/>
       </c>
       <c r="G31" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H31" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I31" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J31" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K31" s="33"/>
@@ -6738,7 +5960,7 @@
         <v>24</v>
       </c>
       <c r="BH31" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI31" s="44"/>
@@ -6762,36 +5984,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU31" s="44"/>
-      <c r="BV31" s="42"/>
-      <c r="BW31" s="43"/>
-      <c r="BX31" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY31" s="44"/>
-      <c r="BZ31" s="42"/>
-      <c r="CA31" s="43"/>
-      <c r="CB31" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC31" s="44"/>
-      <c r="CD31" s="42"/>
-      <c r="CE31" s="43"/>
-      <c r="CF31" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG31" s="44"/>
-      <c r="CH31" s="42"/>
-      <c r="CI31" s="43"/>
-      <c r="CJ31" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="32" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <v>25</v>
       </c>
@@ -6804,19 +5998,19 @@
         <v/>
       </c>
       <c r="G32" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H32" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I32" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J32" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K32" s="33"/>
@@ -6907,7 +6101,7 @@
         <v>25</v>
       </c>
       <c r="BH32" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI32" s="44"/>
@@ -6931,36 +6125,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU32" s="44"/>
-      <c r="BV32" s="42"/>
-      <c r="BW32" s="43"/>
-      <c r="BX32" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY32" s="44"/>
-      <c r="BZ32" s="42"/>
-      <c r="CA32" s="43"/>
-      <c r="CB32" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC32" s="44"/>
-      <c r="CD32" s="42"/>
-      <c r="CE32" s="43"/>
-      <c r="CF32" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG32" s="44"/>
-      <c r="CH32" s="42"/>
-      <c r="CI32" s="43"/>
-      <c r="CJ32" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="33" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <v>26</v>
       </c>
@@ -6973,19 +6139,19 @@
         <v/>
       </c>
       <c r="G33" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H33" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I33" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J33" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K33" s="33"/>
@@ -7076,7 +6242,7 @@
         <v>26</v>
       </c>
       <c r="BH33" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI33" s="44"/>
@@ -7100,36 +6266,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU33" s="44"/>
-      <c r="BV33" s="42"/>
-      <c r="BW33" s="43"/>
-      <c r="BX33" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY33" s="44"/>
-      <c r="BZ33" s="42"/>
-      <c r="CA33" s="43"/>
-      <c r="CB33" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC33" s="44"/>
-      <c r="CD33" s="42"/>
-      <c r="CE33" s="43"/>
-      <c r="CF33" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG33" s="44"/>
-      <c r="CH33" s="42"/>
-      <c r="CI33" s="43"/>
-      <c r="CJ33" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="34" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>27</v>
       </c>
@@ -7142,19 +6280,19 @@
         <v/>
       </c>
       <c r="G34" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H34" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I34" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J34" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K34" s="33"/>
@@ -7245,7 +6383,7 @@
         <v>27</v>
       </c>
       <c r="BH34" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI34" s="44"/>
@@ -7269,36 +6407,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU34" s="44"/>
-      <c r="BV34" s="42"/>
-      <c r="BW34" s="43"/>
-      <c r="BX34" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY34" s="44"/>
-      <c r="BZ34" s="42"/>
-      <c r="CA34" s="43"/>
-      <c r="CB34" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC34" s="44"/>
-      <c r="CD34" s="42"/>
-      <c r="CE34" s="43"/>
-      <c r="CF34" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG34" s="44"/>
-      <c r="CH34" s="42"/>
-      <c r="CI34" s="43"/>
-      <c r="CJ34" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="35" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>28</v>
       </c>
@@ -7311,19 +6421,19 @@
         <v/>
       </c>
       <c r="G35" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H35" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I35" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J35" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K35" s="33"/>
@@ -7414,7 +6524,7 @@
         <v>28</v>
       </c>
       <c r="BH35" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI35" s="44"/>
@@ -7438,36 +6548,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU35" s="44"/>
-      <c r="BV35" s="42"/>
-      <c r="BW35" s="43"/>
-      <c r="BX35" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY35" s="44"/>
-      <c r="BZ35" s="42"/>
-      <c r="CA35" s="43"/>
-      <c r="CB35" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC35" s="44"/>
-      <c r="CD35" s="42"/>
-      <c r="CE35" s="43"/>
-      <c r="CF35" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG35" s="44"/>
-      <c r="CH35" s="42"/>
-      <c r="CI35" s="43"/>
-      <c r="CJ35" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="36" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <v>29</v>
       </c>
@@ -7480,19 +6562,19 @@
         <v/>
       </c>
       <c r="G36" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H36" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I36" s="35" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J36" s="37" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K36" s="33"/>
@@ -7583,7 +6665,7 @@
         <v>29</v>
       </c>
       <c r="BH36" s="32" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI36" s="44"/>
@@ -7607,36 +6689,8 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU36" s="44"/>
-      <c r="BV36" s="42"/>
-      <c r="BW36" s="43"/>
-      <c r="BX36" s="45" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY36" s="44"/>
-      <c r="BZ36" s="42"/>
-      <c r="CA36" s="43"/>
-      <c r="CB36" s="45" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC36" s="44"/>
-      <c r="CD36" s="42"/>
-      <c r="CE36" s="43"/>
-      <c r="CF36" s="45" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG36" s="44"/>
-      <c r="CH36" s="42"/>
-      <c r="CI36" s="43"/>
-      <c r="CJ36" s="45" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="37" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>30</v>
       </c>
@@ -7649,19 +6703,19 @@
         <v/>
       </c>
       <c r="G37" s="50" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H37" s="50" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I37" s="51" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J37" s="53" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K37" s="49"/>
@@ -7752,7 +6806,7 @@
         <v>30</v>
       </c>
       <c r="BH37" s="48" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BI37" s="60"/>
@@ -7776,262 +6830,234 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BU37" s="60"/>
-      <c r="BV37" s="58"/>
-      <c r="BW37" s="59"/>
-      <c r="BX37" s="61" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BY37" s="60"/>
-      <c r="BZ37" s="58"/>
-      <c r="CA37" s="59"/>
-      <c r="CB37" s="61" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="CC37" s="60"/>
-      <c r="CD37" s="58"/>
-      <c r="CE37" s="59"/>
-      <c r="CF37" s="61" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG37" s="60"/>
-      <c r="CH37" s="58"/>
-      <c r="CI37" s="59"/>
-      <c r="CJ37" s="61" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
     </row>
-    <row r="38" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A38" s="88" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="89"/>
       <c r="C38" s="62" t="str">
-        <f t="shared" ref="C38:AY38" si="27">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
+        <f t="shared" ref="C38:AY38" si="23">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
       </c>
       <c r="D38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="E38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="F38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="G38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="H38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="L38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="R38" s="66" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="U38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="V38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="W38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="X38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Y38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Z38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AA38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AB38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AC38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AD38" s="66" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AE38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AF38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AG38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AH38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AI38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AJ38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AK38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AL38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AM38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AN38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AO38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AP38" s="66" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AQ38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AR38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AS38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AT38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AU38" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AV38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AW38" s="64" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AX38" s="65" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AY38" s="63" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AZ38" s="63" t="str">
-        <f t="shared" ref="AZ38:BF38" si="28">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ38:BF38" si="24">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA38" s="64" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BB38" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BC38" s="67" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BD38" s="68" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BE38" s="69" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BF38" s="70" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BG38" s="88" t="s">
@@ -8039,345 +7065,281 @@
       </c>
       <c r="BH38" s="89"/>
       <c r="BI38" s="62" t="str">
-        <f t="shared" ref="BI38:BT38" si="29">IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
+        <f t="shared" ref="BI38:BT38" si="25">IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ38" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BK38" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BL38" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BM38" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BN38" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BO38" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BP38" s="65" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BQ38" s="62" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BR38" s="63" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BS38" s="64" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BT38" s="65" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BU38" s="62" t="str">
-        <f t="shared" ref="BU38:CJ38" si="30">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV38" s="63" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="BW38" s="64" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="BX38" s="65" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="BY38" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="BZ38" s="63" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CA38" s="64" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CB38" s="65" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CC38" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CD38" s="63" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CE38" s="64" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CF38" s="65" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CG38" s="62" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CH38" s="63" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CI38" s="64" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="CJ38" s="65" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A39" s="90" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="91"/>
       <c r="C39" s="62" t="str">
-        <f t="shared" ref="C39:AY39" si="31">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
+        <f t="shared" ref="C39:AY39" si="26">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
         <v/>
       </c>
       <c r="D39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="F39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="G39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="H39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="I39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="K39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="L39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="R39" s="66" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="T39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="U39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="V39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="W39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="X39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Y39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Z39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AB39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AC39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AD39" s="66" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AF39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AG39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AH39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AI39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AJ39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AK39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AL39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AM39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AN39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AO39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AP39" s="66" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AQ39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AR39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AS39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AT39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AU39" s="62" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AV39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AW39" s="64" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AX39" s="65" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AY39" s="63" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AZ39" s="63" t="str">
-        <f t="shared" ref="AZ39:BF39" si="32">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ39:BF39" si="27">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA39" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BB39" s="66" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BC39" s="67" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD39" s="68" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BE39" s="69" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF39" s="70" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BG39" s="90" t="s">
@@ -8385,345 +7347,281 @@
       </c>
       <c r="BH39" s="91"/>
       <c r="BI39" s="62" t="str">
-        <f t="shared" ref="BI39:BT39" si="33">IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
+        <f t="shared" ref="BI39:BT39" si="28">IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ39" s="63" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BK39" s="64" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BL39" s="65" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BM39" s="62" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BN39" s="63" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BO39" s="64" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BP39" s="65" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BQ39" s="62" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BR39" s="63" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BS39" s="64" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BT39" s="65" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BU39" s="62" t="str">
-        <f t="shared" ref="BU39:CJ39" si="34">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV39" s="63" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BW39" s="64" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BX39" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BY39" s="62" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BZ39" s="63" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CA39" s="64" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CB39" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CC39" s="62" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CD39" s="63" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CE39" s="64" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CF39" s="65" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CG39" s="62" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CH39" s="63" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CI39" s="64" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="CJ39" s="65" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A40" s="90" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="91"/>
       <c r="C40" s="62" t="str">
-        <f t="shared" ref="C40:AY40" si="35">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
+        <f t="shared" ref="C40:AY40" si="29">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
         <v/>
       </c>
       <c r="D40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="E40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="F40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="G40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="H40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="I40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J40" s="66" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="L40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="R40" s="66" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="S40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="T40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="U40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="V40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="W40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="X40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Y40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Z40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AA40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AB40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AC40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD40" s="66" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AF40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AG40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AH40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AI40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AJ40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AK40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AL40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AM40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AN40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AO40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AP40" s="66" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AQ40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AR40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AS40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AT40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AU40" s="62" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AV40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AW40" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AX40" s="65" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AY40" s="63" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AZ40" s="63" t="str">
-        <f t="shared" ref="AZ40:BF40" si="36">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ40:BF40" si="30">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA40" s="64" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BB40" s="66" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BC40" s="67" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BD40" s="68" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BE40" s="69" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BF40" s="70" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BG40" s="90" t="s">
@@ -8731,345 +7629,281 @@
       </c>
       <c r="BH40" s="91"/>
       <c r="BI40" s="62" t="str">
-        <f t="shared" ref="BI40:BT40" si="37">IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
+        <f t="shared" ref="BI40:BT40" si="31">IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ40" s="63" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BK40" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BL40" s="65" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BM40" s="62" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BN40" s="63" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BO40" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BP40" s="65" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BQ40" s="62" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BR40" s="63" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BS40" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BT40" s="65" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BU40" s="62" t="str">
-        <f t="shared" ref="BU40:CJ40" si="38">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV40" s="63" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BW40" s="64" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BX40" s="65" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BY40" s="62" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BZ40" s="63" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CA40" s="64" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CB40" s="65" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CC40" s="62" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CD40" s="63" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CE40" s="64" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CF40" s="65" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CG40" s="62" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CH40" s="63" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CI40" s="64" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="CJ40" s="65" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A41" s="90" t="s">
         <v>14</v>
       </c>
       <c r="B41" s="91"/>
       <c r="C41" s="62" t="str">
-        <f t="shared" ref="C41:AY41" si="39">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
+        <f t="shared" ref="C41:AY41" si="32">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
         <v/>
       </c>
       <c r="D41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="E41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="F41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="G41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="H41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="I41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="N41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="O41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="R41" s="66" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="S41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="T41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="U41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="V41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="W41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="X41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Y41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Z41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AA41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AB41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AC41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AD41" s="66" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AE41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AF41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AG41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AH41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AI41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AJ41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AK41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AL41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AN41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AO41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AP41" s="66" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AQ41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AR41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AS41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AT41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AU41" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AV41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AW41" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AX41" s="65" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AY41" s="63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AZ41" s="63" t="str">
-        <f t="shared" ref="AZ41:BF41" si="40">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
+        <f t="shared" ref="AZ41:BF41" si="33">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
         <v/>
       </c>
       <c r="BA41" s="64" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BB41" s="66" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BC41" s="67" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BD41" s="68" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BE41" s="69" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BF41" s="70" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BG41" s="90" t="s">
@@ -9077,345 +7911,281 @@
       </c>
       <c r="BH41" s="91"/>
       <c r="BI41" s="62" t="str">
-        <f t="shared" ref="BI41:BT41" si="41">IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
+        <f t="shared" ref="BI41:BT41" si="34">IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
         <v/>
       </c>
       <c r="BJ41" s="63" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BK41" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BL41" s="65" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BM41" s="62" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BN41" s="63" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BO41" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BP41" s="65" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BQ41" s="62" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BR41" s="63" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BS41" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BT41" s="65" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="BU41" s="62" t="str">
-        <f t="shared" ref="BU41:CJ41" si="42">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV41" s="63" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="BW41" s="64" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="BX41" s="65" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="BY41" s="62" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="BZ41" s="63" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CA41" s="64" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CB41" s="65" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CC41" s="62" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CD41" s="63" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CE41" s="64" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CF41" s="65" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CG41" s="62" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CH41" s="63" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CI41" s="64" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CJ41" s="65" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A42" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B42" s="79"/>
       <c r="C42" s="2" t="str">
-        <f t="shared" ref="C42:AY42" si="43">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
+        <f t="shared" ref="C42:AY42" si="35">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
         <v/>
       </c>
       <c r="D42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="E42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="F42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="H42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="J42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="L42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R42" s="6" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="S42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="T42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="U42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="W42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="X42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Y42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Z42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AB42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AC42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AD42" s="6" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AE42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AF42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AG42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AH42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AI42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AJ42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AK42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AL42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AM42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AN42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AO42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AP42" s="6" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AQ42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AR42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AS42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AT42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AU42" s="2" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AV42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AW42" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AX42" s="5" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AY42" s="3" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AZ42" s="3" t="str">
-        <f t="shared" ref="AZ42:BF42" si="44">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
+        <f t="shared" ref="AZ42:BF42" si="36">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
         <v/>
       </c>
       <c r="BA42" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BB42" s="6" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BC42" s="7" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BD42" s="8" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BE42" s="9" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BF42" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG42" s="78" t="s">
@@ -9423,119 +8193,55 @@
       </c>
       <c r="BH42" s="79"/>
       <c r="BI42" s="2" t="str">
-        <f t="shared" ref="BI42:BT42" si="45">IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
+        <f t="shared" ref="BI42:BT42" si="37">IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
         <v/>
       </c>
       <c r="BJ42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BK42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BL42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BM42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BN42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BO42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BP42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BQ42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BR42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BS42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="BT42" s="5" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="BU42" s="2" t="str">
-        <f t="shared" ref="BU42:CJ42" si="46">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
-        <v/>
-      </c>
-      <c r="BV42" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BW42" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BX42" s="5" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BY42" s="2" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="BZ42" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CA42" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CB42" s="5" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CC42" s="2" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CD42" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CE42" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CF42" s="5" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CG42" s="2" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CH42" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CI42" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CJ42" s="5" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:82" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A50" s="76" t="s">
         <v>24</v>
       </c>
@@ -9556,24 +8262,24 @@
       <c r="P50" s="77"/>
       <c r="Q50" s="77"/>
       <c r="R50" s="77"/>
-      <c r="S50" s="76" t="s">
+      <c r="S50" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="T50" s="76"/>
-      <c r="U50" s="76"/>
-      <c r="V50" s="76"/>
-      <c r="W50" s="76"/>
-      <c r="X50" s="76"/>
-      <c r="Y50" s="76"/>
-      <c r="Z50" s="76"/>
-      <c r="AA50" s="76"/>
-      <c r="AB50" s="76"/>
-      <c r="AC50" s="76"/>
-      <c r="AD50" s="76"/>
-      <c r="AE50" s="76"/>
-      <c r="AF50" s="76"/>
-      <c r="AG50" s="76"/>
-      <c r="AH50" s="76"/>
+      <c r="T50" s="72"/>
+      <c r="U50" s="72"/>
+      <c r="V50" s="72"/>
+      <c r="W50" s="72"/>
+      <c r="X50" s="72"/>
+      <c r="Y50" s="72"/>
+      <c r="Z50" s="72"/>
+      <c r="AA50" s="72"/>
+      <c r="AB50" s="72"/>
+      <c r="AC50" s="72"/>
+      <c r="AD50" s="72"/>
+      <c r="AE50" s="72"/>
+      <c r="AF50" s="72"/>
+      <c r="AG50" s="72"/>
+      <c r="AH50" s="72"/>
       <c r="AI50" s="1"/>
       <c r="AK50" s="76" t="s">
         <v>24</v>
@@ -9595,35 +8301,37 @@
       <c r="AZ50" s="77"/>
       <c r="BA50" s="77"/>
       <c r="BB50" s="77"/>
-      <c r="BH50" s="74" t="s">
+      <c r="BH50" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="BI50" s="76"/>
-      <c r="BJ50" s="76"/>
-      <c r="BK50" s="72"/>
-      <c r="BL50" s="72"/>
-      <c r="BM50" s="76" t="s">
-        <v>24</v>
-      </c>
+      <c r="BI50" s="72"/>
+      <c r="BJ50" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="BK50" s="76"/>
+      <c r="BL50" s="76"/>
+      <c r="BM50" s="76"/>
       <c r="BN50" s="76"/>
       <c r="BO50" s="76"/>
       <c r="BP50" s="76"/>
       <c r="BQ50" s="76"/>
-      <c r="BR50" s="76"/>
+      <c r="BR50" s="76" t="s">
+        <v>24</v>
+      </c>
       <c r="BS50" s="76"/>
       <c r="BT50" s="76"/>
       <c r="BU50" s="76"/>
-      <c r="BV50" s="72"/>
-      <c r="BW50" s="72"/>
-      <c r="BX50" s="72"/>
-      <c r="BY50" s="72"/>
-      <c r="BZ50" s="72"/>
-      <c r="CA50" s="72"/>
-      <c r="CB50" s="72"/>
-      <c r="CC50" s="72"/>
-      <c r="CD50" s="72"/>
+      <c r="BV50" s="76"/>
+      <c r="BW50" s="76"/>
+      <c r="BX50" s="76"/>
+      <c r="BY50" s="76"/>
+      <c r="BZ50" s="76"/>
+      <c r="CA50" s="71"/>
+      <c r="CB50" s="71"/>
+      <c r="CC50" s="71"/>
+      <c r="CD50" s="71"/>
     </row>
-    <row r="51" spans="1:82" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A51" s="77" t="s">
         <v>35</v>
       </c>
@@ -9644,24 +8352,24 @@
       <c r="P51" s="77"/>
       <c r="Q51" s="77"/>
       <c r="R51" s="77"/>
-      <c r="S51" s="77" t="s">
+      <c r="S51" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="T51" s="77"/>
-      <c r="U51" s="77"/>
-      <c r="V51" s="77"/>
-      <c r="W51" s="77"/>
-      <c r="X51" s="77"/>
-      <c r="Y51" s="77"/>
-      <c r="Z51" s="77"/>
-      <c r="AA51" s="77"/>
-      <c r="AB51" s="77"/>
-      <c r="AC51" s="77"/>
-      <c r="AD51" s="77"/>
-      <c r="AE51" s="77"/>
-      <c r="AF51" s="77"/>
-      <c r="AG51" s="77"/>
-      <c r="AH51" s="77"/>
+      <c r="T51" s="71"/>
+      <c r="U51" s="71"/>
+      <c r="V51" s="71"/>
+      <c r="W51" s="71"/>
+      <c r="X51" s="71"/>
+      <c r="Y51" s="71"/>
+      <c r="Z51" s="71"/>
+      <c r="AA51" s="71"/>
+      <c r="AB51" s="71"/>
+      <c r="AC51" s="71"/>
+      <c r="AD51" s="71"/>
+      <c r="AE51" s="71"/>
+      <c r="AF51" s="71"/>
+      <c r="AG51" s="71"/>
+      <c r="AH51" s="71"/>
       <c r="AI51" s="1"/>
       <c r="AK51" s="77" t="s">
         <v>34</v>
@@ -9686,133 +8394,131 @@
       <c r="BE51" t="s">
         <v>36</v>
       </c>
-      <c r="BH51" s="75" t="s">
+      <c r="BH51" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="BI51" s="77"/>
-      <c r="BJ51" s="77"/>
-      <c r="BK51" s="72"/>
-      <c r="BL51" s="72"/>
-      <c r="BM51" s="77" t="s">
-        <v>34</v>
-      </c>
+      <c r="BI51" s="71"/>
+      <c r="BJ51" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="BK51" s="77"/>
+      <c r="BL51" s="77"/>
+      <c r="BM51" s="77"/>
       <c r="BN51" s="77"/>
       <c r="BO51" s="77"/>
       <c r="BP51" s="77"/>
       <c r="BQ51" s="77"/>
-      <c r="BR51" s="77"/>
+      <c r="BR51" s="77" t="s">
+        <v>34</v>
+      </c>
       <c r="BS51" s="77"/>
       <c r="BT51" s="77"/>
       <c r="BU51" s="77"/>
-      <c r="BV51" s="72"/>
-      <c r="BW51" s="72"/>
-      <c r="BX51" s="72"/>
-      <c r="BY51" s="72"/>
-      <c r="BZ51" s="71" t="s">
-        <v>37</v>
-      </c>
-      <c r="CA51" s="72"/>
-      <c r="CB51" s="72"/>
-      <c r="CC51" s="72"/>
-      <c r="CD51" s="72"/>
+      <c r="BV51" s="77"/>
+      <c r="BW51" s="77"/>
+      <c r="BX51" s="77"/>
+      <c r="BY51" s="77"/>
+      <c r="BZ51" s="77"/>
+      <c r="CA51" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="CB51" s="71"/>
+      <c r="CC51" s="71"/>
+      <c r="CD51" s="71"/>
     </row>
-    <row r="53" spans="1:82" x14ac:dyDescent="0.3">
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="72"/>
-      <c r="J53" s="72"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="72"/>
-      <c r="M53" s="72"/>
-      <c r="N53" s="72"/>
-      <c r="O53" s="72"/>
-      <c r="P53" s="72"/>
-      <c r="Q53" s="72"/>
-      <c r="R53" s="72"/>
-      <c r="S53" s="72"/>
-      <c r="T53" s="72"/>
-      <c r="U53" s="72"/>
-      <c r="V53" s="72"/>
-      <c r="W53" s="72"/>
-      <c r="X53" s="72"/>
-      <c r="Y53" s="72"/>
-      <c r="Z53" s="73"/>
-      <c r="AA53" s="72"/>
-      <c r="AB53" s="72"/>
-      <c r="AC53" s="72"/>
-      <c r="AD53" s="72"/>
-      <c r="AE53" s="72"/>
-      <c r="AF53" s="72"/>
-      <c r="AG53" s="72"/>
-      <c r="AH53" s="72"/>
-      <c r="AI53" s="72"/>
-      <c r="AJ53" s="72"/>
-      <c r="AK53" s="72"/>
-      <c r="AL53" s="72"/>
-      <c r="AM53" s="72"/>
-      <c r="AN53" s="72"/>
-      <c r="AO53" s="72"/>
-      <c r="AP53" s="72"/>
+    <row r="53" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="72"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="71"/>
+      <c r="K53" s="71"/>
+      <c r="L53" s="71"/>
+      <c r="M53" s="71"/>
+      <c r="N53" s="71"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="71"/>
+      <c r="S53" s="71"/>
+      <c r="T53" s="71"/>
+      <c r="U53" s="71"/>
+      <c r="V53" s="71"/>
+      <c r="W53" s="71"/>
+      <c r="X53" s="71"/>
+      <c r="Y53" s="71"/>
+      <c r="Z53" s="72"/>
+      <c r="AA53" s="71"/>
+      <c r="AB53" s="71"/>
+      <c r="AC53" s="71"/>
+      <c r="AD53" s="71"/>
+      <c r="AE53" s="71"/>
+      <c r="AF53" s="71"/>
+      <c r="AG53" s="71"/>
+      <c r="AH53" s="71"/>
+      <c r="AI53" s="71"/>
+      <c r="AJ53" s="71"/>
+      <c r="AK53" s="71"/>
+      <c r="AL53" s="71"/>
+      <c r="AM53" s="71"/>
+      <c r="AN53" s="71"/>
+      <c r="AO53" s="71"/>
+      <c r="AP53" s="71"/>
     </row>
-    <row r="54" spans="1:82" x14ac:dyDescent="0.3">
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="72"/>
-      <c r="G54" s="72"/>
-      <c r="H54" s="72"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="72"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="72"/>
-      <c r="M54" s="72"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="72"/>
-      <c r="P54" s="72"/>
-      <c r="Q54" s="72"/>
-      <c r="R54" s="72"/>
-      <c r="S54" s="72"/>
-      <c r="T54" s="72"/>
-      <c r="U54" s="72"/>
-      <c r="V54" s="72"/>
-      <c r="W54" s="72"/>
-      <c r="X54" s="72"/>
-      <c r="Y54" s="72"/>
-      <c r="Z54" s="72"/>
-      <c r="AA54" s="72"/>
-      <c r="AB54" s="72"/>
-      <c r="AC54" s="72"/>
-      <c r="AD54" s="72"/>
-      <c r="AE54" s="72"/>
-      <c r="AF54" s="72"/>
-      <c r="AG54" s="72"/>
-      <c r="AH54" s="72"/>
-      <c r="AI54" s="72"/>
-      <c r="AJ54" s="72"/>
-      <c r="AK54" s="72"/>
-      <c r="AL54" s="72"/>
-      <c r="AM54" s="72"/>
-      <c r="AN54" s="72"/>
-      <c r="AO54" s="72"/>
-      <c r="AP54" s="72"/>
+    <row r="54" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="71"/>
+      <c r="K54" s="71"/>
+      <c r="L54" s="71"/>
+      <c r="M54" s="71"/>
+      <c r="N54" s="71"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="71"/>
+      <c r="S54" s="71"/>
+      <c r="T54" s="71"/>
+      <c r="U54" s="71"/>
+      <c r="V54" s="71"/>
+      <c r="W54" s="71"/>
+      <c r="X54" s="71"/>
+      <c r="Y54" s="71"/>
+      <c r="Z54" s="71"/>
+      <c r="AA54" s="71"/>
+      <c r="AB54" s="71"/>
+      <c r="AC54" s="71"/>
+      <c r="AD54" s="71"/>
+      <c r="AE54" s="71"/>
+      <c r="AF54" s="71"/>
+      <c r="AG54" s="71"/>
+      <c r="AH54" s="71"/>
+      <c r="AI54" s="71"/>
+      <c r="AJ54" s="71"/>
+      <c r="AK54" s="71"/>
+      <c r="AL54" s="71"/>
+      <c r="AM54" s="71"/>
+      <c r="AN54" s="71"/>
+      <c r="AO54" s="71"/>
+      <c r="AP54" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="BU6:BX6"/>
-    <mergeCell ref="BY6:CB6"/>
-    <mergeCell ref="CC6:CF6"/>
-    <mergeCell ref="CG6:CJ6"/>
-    <mergeCell ref="BG2:CJ2"/>
-    <mergeCell ref="BG3:CJ3"/>
-    <mergeCell ref="BG4:CJ4"/>
-    <mergeCell ref="BG5:CJ5"/>
+  <mergeCells count="47">
     <mergeCell ref="BI6:BL6"/>
     <mergeCell ref="BM6:BP6"/>
     <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="BG2:BT2"/>
+    <mergeCell ref="BG3:BT3"/>
+    <mergeCell ref="BG4:BT4"/>
+    <mergeCell ref="BG5:BT5"/>
     <mergeCell ref="BG6:BG7"/>
     <mergeCell ref="BH6:BH7"/>
     <mergeCell ref="BG38:BH38"/>
@@ -9845,42 +8551,29 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="BM50:BU50"/>
-    <mergeCell ref="BM51:BU51"/>
     <mergeCell ref="A50:R50"/>
     <mergeCell ref="AK50:BB50"/>
     <mergeCell ref="A51:R51"/>
     <mergeCell ref="AK51:BB51"/>
-    <mergeCell ref="S50:AH50"/>
-    <mergeCell ref="S51:AH51"/>
-    <mergeCell ref="BI50:BJ50"/>
-    <mergeCell ref="BI51:BJ51"/>
+    <mergeCell ref="BR50:BZ50"/>
+    <mergeCell ref="BR51:BZ51"/>
+    <mergeCell ref="BJ50:BQ50"/>
+    <mergeCell ref="BJ51:BQ51"/>
   </mergeCells>
+  <phoneticPr fontId="28" type="noConversion"/>
   <conditionalFormatting sqref="C8:BF37">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI8:BT37">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BU8:CB37">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CC8:CJ37">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.21249999999999999" right="0.25" top="0.21875" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.21249999999999999" right="0.25" top="0.51666666666666672" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="10000" scale="62" fitToWidth="2" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="58" max="54" man="1"/>
